--- a/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
+++ b/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gevoeligheid" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Panteia-parameters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gevoeligheid" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="€#,##0;(€#,##0);-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="€#,##0.00;(€#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="€#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="€#,##0;(€#,##0);-"/>
+    <numFmt numFmtId="167" formatCode="€#,##0.00;(€#,##0.00);-"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -40,7 +42,7 @@
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="00808080"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -69,20 +71,19 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -108,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -116,16 +117,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00808080"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,21 +130,38 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,27 +527,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E63"/>
+  <dimension ref="B1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="74" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="96" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>TCO-model elektrische vrachtwagens — AanZET 2026</t>
+          <t>TCO elektrische vrachtwagens — gekalibreerd op TCO-ZET-Vracht v7.3 (Panteia / Topsector Logistiek)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>A. Baas Potplantenkwekerij B.V. — 2 trucks, categorie N3</t>
+          <t>A. Baas Potplantenkwekerij B.V. — 2 trucks · AanZET 2026 + SPRILA</t>
         </is>
       </c>
     </row>
@@ -546,7 +559,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Geel met blauwe tekst = zelf invullen. Zwarte tekst = formule, niet overschrijven.</t>
+          <t>Geel/blauw = zelf invullen · zwart = formule · groen = automatisch uit blad Panteia-parameters</t>
         </is>
       </c>
     </row>
@@ -559,6 +572,8 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
@@ -579,9 +594,9 @@
       <c r="C8" s="7" t="n">
         <v>150000</v>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Afgeleid uit 2 x 300-400 km/dag x ca. 230 dagen — VERVANGEN door werkelijke cijfers</t>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>VERVANGEN door werkelijk jaarkilometrage — grootste hefboom in het model</t>
         </is>
       </c>
     </row>
@@ -591,618 +606,840 @@
           <t>Ondernemingsgrootte</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Kies: Klein / Middelgroot / Groot. Toets geldt voor de HELE groep, geconsolideerd</t>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Klein / Middelgroot / Groot — geldt voor de HELE groep, geconsolideerd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Chassisprijs e-truck (excl. opbouw, excl. btw)</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>280000</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>AANNAME — grondslag voor de subsidie, opvragen bij de dealer</t>
+          <t>Voertuigtype</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Zware trekker z/opl</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Kies uit blad Panteia-parameters. Stuurt verbruik, onderhoud, banden en AanZET-categorie aan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Vergelijkbaar dieselchassis (excl. btw)</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>AANNAME</t>
+          <t>Dieselverbruik — 1 op ...</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Opgave Kwekerij Baas</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Dieselverbruik (l per 100 km)</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>AANNAME — 40-tons combinatie</t>
-        </is>
+          <t xml:space="preserve">  → liter per km</t>
+        </is>
+      </c>
+      <c r="C12" s="10">
+        <f>IF($C$11=0,0,1/$C$11)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Dieselprijs (excl. btw, per liter)</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>AANNAME</t>
+          <t>Bruto aanschafprijs e-truck</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>280000</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>AANNAME — opvragen bij de dealer. Grondslag voor AanZET</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Stroomverbruik (kWh per km)</t>
+          <t>Bruto aanschafprijs vergelijkbare diesel</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>AANNAME — verhoog met 5-10% voor laadverliezen</t>
+        <v>120000</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>AANNAME. Bepaalt de meerprijs en daarmee het staatssteunplafond</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Stroomprijs all-in (per kWh)</t>
+          <t>Netto dieselprijs per liter</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>AANNAME — levering + energiebelasting + opslagen + variabel netbeheer</t>
+        <v>1.6063</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Panteia Parameters D4+D5: kale prijs €1.09 + accijns €0.5163</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Onderhoud diesel (per km)</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>AANNAME</t>
+          <t>Aandeel eigen opwek (zon + accu)</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Panteia Parameters J46</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Onderhoud elektrisch (per km)</t>
+          <t>Prijs eigen opwek per kWh</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>AANNAME</t>
+        <v>0.11</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Panteia Parameters J47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Vrachtwagenheffing diesel (per km)</t>
+          <t>Prijs netstroom per kWh</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>Bron: tarief per 1 juli 2026, gemiddelde</t>
+        <v>0.21537</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Panteia Parameters D6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Vrachtwagenheffing zero-emissie (per km)</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Bron: ca. 80% korting t.o.v. Euro VI diesel</t>
-        </is>
+          <t xml:space="preserve">  → gemengde stroomprijs</t>
+        </is>
+      </c>
+      <c r="C19" s="14">
+        <f>$C$16*$C$17+(1-$C$16)*$C$18</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Vennootschapsbelasting</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Tarief 2026</t>
+          <t>Vrachtwagenheffing diesel (€/km)</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Per 1 juli 2026 — zit NIET in de Panteia-tool v7.3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>EIA-aftrekpercentage</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>EIA 2026</t>
+          <t>Vrachtwagenheffing zero-emissie (€/km)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Per 1 juli 2026 — circa 80% korting</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Investering laadinfrastructuur (excl. btw)</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>461500</v>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Offerte Draccu DR283: accu 1.045 kWh + 3x DC 240 kW</t>
+          <t>Extra chauffeurskosten elektrisch per jaar</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>3655</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Wachttijd bij laden. Panteia rekent +4,1% (E118 vs D118). Schaalt mee met de inzet</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>SPRILA-subsidie laadinfrastructuur</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>178000</v>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Aanvraag juli 2026</t>
+          <t>Vennootschapsbelasting</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Tarief 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>EIA-aftrekpercentage</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>EIA 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2. AANZET-PERCENTAGES CATEGORIE N3</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>EIA-grondslag = volledige aanschafprijs?</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Nee = alleen de meerprijs (voorzichtig). Ja = hele aanschafprijs, zoals Panteia bij MIA doet</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Ondernemingsgrootte</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Maximum per voertuig</t>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Investering laadinfrastructuur</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>461500</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Offerte Draccu DR283: accu 1.045 kWh + 3x DC 240 kW</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Klein</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>115200</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Middelgroot</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>83200</v>
+          <t>SPRILA-subsidie</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>178000</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Volgens de RVO-bedragen 2026. LET OP: de Panteia-tool hanteert afwijkende SPRILA-bedragen</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Groot</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>43900</v>
-      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2. UIT HET VOERTUIGTYPE (Panteia)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Niet geverifieerd tegen de regelingstekst — controleer op rvo.nl/aanzet</t>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>AanZET-categorie</t>
+        </is>
+      </c>
+      <c r="C30" s="15">
+        <f>INDEX('Panteia-parameters'!$J$6:$J$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Panteia-verbruik diesel (l/km) — referentie</t>
+        </is>
+      </c>
+      <c r="C31" s="16">
+        <f>INDEX('Panteia-parameters'!$C$6:$C$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
+        <v/>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Ter vergelijking met jullie eigen 1 op-cijfer hierboven</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>3. AANZET-SUBSIDIE</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Stroomverbruik e-truck (kWh/km)</t>
+        </is>
+      </c>
+      <c r="C32" s="17">
+        <f>INDEX('Panteia-parameters'!$D$6:$D$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
+        <v/>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Inclusief laadverliezen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Subsidiepercentage van toepassing</t>
+          <t>Onderhoud diesel (€/km)</t>
         </is>
       </c>
       <c r="C33" s="18">
-        <f>INDEX($C$27:$C$29,MATCH($C$9,$B$27:$B$29,0))</f>
+        <f>INDEX('Panteia-parameters'!$E$6:$E$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Maximum per voertuig</t>
-        </is>
-      </c>
-      <c r="C34" s="19">
-        <f>INDEX($D$27:$D$29,MATCH($C$9,$B$27:$B$29,0))</f>
+          <t>Onderhoud elektrisch (€/km)</t>
+        </is>
+      </c>
+      <c r="C34" s="18">
+        <f>INDEX('Panteia-parameters'!$F$6:$F$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>AanZET per truck</t>
+          <t>Reparaties per jaar (beide)</t>
         </is>
       </c>
       <c r="C35" s="19">
-        <f>MIN($C$10*C33,C34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>Percentage x chassisprijs, afgetopt op het maximum</t>
-        </is>
+        <f>INDEX('Panteia-parameters'!$G$6:$G$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>AanZET totaal</t>
-        </is>
-      </c>
-      <c r="C36" s="20">
-        <f>C35*$C$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>4. EXTRA INVESTERING TEN OPZICHTE VAN DIESEL</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
+          <t>Banden (€/km, beide)</t>
+        </is>
+      </c>
+      <c r="C36" s="18">
+        <f>INDEX('Panteia-parameters'!$H$6:$H$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Motorrijtuigenbelasting per jaar</t>
+        </is>
+      </c>
+      <c r="C37" s="19">
+        <f>INDEX('Panteia-parameters'!$I$6:$I$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
+        <v/>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Gelijk verondersteld voor diesel en elektrisch — valt vanaf 1-7-2026 terug naar het EU-minimum</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Meerkosten e-truck per truck</t>
-        </is>
-      </c>
-      <c r="C39" s="19">
-        <f>$C$10-$C$11</f>
-        <v/>
-      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>3. AANZET-SUBSIDIE</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>EIA-grondslag per truck</t>
-        </is>
-      </c>
-      <c r="C40" s="19">
-        <f>MAX(0,C39-C35)</f>
-        <v/>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>Meerkosten minus subsidie. Voorzichtige aanname — zie doc §4</t>
-        </is>
+          <t>Subsidiepercentage</t>
+        </is>
+      </c>
+      <c r="C40" s="20">
+        <f>SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,$C$30,'Panteia-parameters'!$D$16:$D$27,$C$9)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>EIA-voordeel per truck (kaseffect)</t>
-        </is>
-      </c>
-      <c r="C41" s="19">
-        <f>C40*$C$21*$C$20</f>
+          <t>Maximum per voertuig</t>
+        </is>
+      </c>
+      <c r="C41" s="21">
+        <f>SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,$C$30,'Panteia-parameters'!$D$16:$D$27,$C$9)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Netto meerkosten per truck</t>
-        </is>
-      </c>
-      <c r="C42" s="19">
-        <f>C39-C35-C41</f>
+          <t>Meerprijs t.o.v. diesel</t>
+        </is>
+      </c>
+      <c r="C42" s="21">
+        <f>MAX(0,$C$13-$C$14)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Netto meerkosten alle trucks</t>
-        </is>
-      </c>
-      <c r="C43" s="19">
-        <f>C42*$C$7</f>
+          <t>Staatssteunplafond (% van meerprijs)</t>
+        </is>
+      </c>
+      <c r="C43" s="20">
+        <f>INDEX('Panteia-parameters'!$D$31:$D$33,MATCH($C$9,'Panteia-parameters'!$C$31:$C$33,0))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Laadinfrastructuur na SPRILA</t>
-        </is>
-      </c>
-      <c r="C44" s="19">
-        <f>$C$22-$C$23</f>
+          <t>Staatssteunplafond in euro</t>
+        </is>
+      </c>
+      <c r="C44" s="21">
+        <f>C43*C42</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>TOTALE EXTRA INVESTERING</t>
-        </is>
-      </c>
-      <c r="C45" s="20">
-        <f>C43+C44</f>
+          <t>AanZET per truck</t>
+        </is>
+      </c>
+      <c r="C45" s="22">
+        <f>MIN($C$13*C40,C41,C44)</f>
+        <v/>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Drie plafonds tegelijk — dezelfde MIN-constructie als M2-Subsidie!B20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>AanZET totaal</t>
+        </is>
+      </c>
+      <c r="C46" s="22">
+        <f>C45*$C$7</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>5. JAARLIJKSE EXPLOITATIEKOSTEN PER TRUCK</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Diesel — brandstof</t>
-        </is>
-      </c>
-      <c r="C48" s="19">
-        <f>$C$8*$C$12/100*$C$13</f>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Welk plafond bijt?</t>
+        </is>
+      </c>
+      <c r="C47" s="23">
+        <f>IF(C45=C44,"staatssteunplafond",IF(C45=C41,"maximum per voertuig","percentage"))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Diesel — vrachtwagenheffing</t>
-        </is>
-      </c>
-      <c r="C49" s="19">
-        <f>$C$8*$C$18</f>
-        <v/>
-      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>4. EXTRA INVESTERING TEN OPZICHTE VAN DIESEL</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Diesel — onderhoud</t>
-        </is>
-      </c>
-      <c r="C50" s="19">
-        <f>$C$8*$C$16</f>
+          <t>Meerprijs per truck</t>
+        </is>
+      </c>
+      <c r="C50" s="21">
+        <f>C42</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Diesel totaal</t>
-        </is>
-      </c>
-      <c r="C51" s="20">
-        <f>SUM(C48:C50)</f>
+          <t>EIA-grondslag per truck</t>
+        </is>
+      </c>
+      <c r="C51" s="21">
+        <f>MAX(0,IF($C$25="Ja",$C$13,C50)-C45)</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch — stroom</t>
-        </is>
-      </c>
-      <c r="C52" s="19">
-        <f>$C$8*$C$14*$C$15</f>
+          <t>EIA-voordeel per truck (kaseffect)</t>
+        </is>
+      </c>
+      <c r="C52" s="21">
+        <f>C51*$C$24*$C$23</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch — vrachtwagenheffing</t>
-        </is>
-      </c>
-      <c r="C53" s="19">
-        <f>$C$8*$C$19</f>
+          <t>Netto meerprijs per truck</t>
+        </is>
+      </c>
+      <c r="C53" s="21">
+        <f>C50-C45-C52</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch — onderhoud</t>
-        </is>
-      </c>
-      <c r="C54" s="19">
-        <f>$C$8*$C$17</f>
+          <t>Netto meerprijs alle trucks</t>
+        </is>
+      </c>
+      <c r="C54" s="21">
+        <f>C53*$C$7</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch totaal</t>
-        </is>
-      </c>
-      <c r="C55" s="20">
-        <f>SUM(C52:C54)</f>
+          <t>Laadinfrastructuur na SPRILA</t>
+        </is>
+      </c>
+      <c r="C55" s="21">
+        <f>$C$26-$C$27</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Besparing per truck per jaar</t>
-        </is>
-      </c>
-      <c r="C56" s="19">
-        <f>C51-C55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Besparing alle trucks per jaar</t>
-        </is>
-      </c>
-      <c r="C57" s="20">
-        <f>C56*$C$7</f>
-        <v/>
-      </c>
+          <t>TOTALE EXTRA INVESTERING</t>
+        </is>
+      </c>
+      <c r="C56" s="22">
+        <f>C54+C55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>5. JAARLIJKSE EXPLOITATIEKOSTEN PER TRUCK</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>6. UITKOMST</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Diesel — brandstof</t>
+        </is>
+      </c>
+      <c r="C59" s="21">
+        <f>$C$8*$C$12*$C$15</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Totale extra investering</t>
-        </is>
-      </c>
-      <c r="C60" s="19">
-        <f>C45</f>
+          <t>Diesel — vrachtwagenheffing</t>
+        </is>
+      </c>
+      <c r="C60" s="21">
+        <f>$C$8*$C$20</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Besparing per jaar</t>
-        </is>
-      </c>
-      <c r="C61" s="19">
-        <f>C57</f>
+          <t>Diesel — onderhoud</t>
+        </is>
+      </c>
+      <c r="C61" s="21">
+        <f>$C$8*C33</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Terugverdientijd (jaren)</t>
+          <t>Diesel — banden</t>
         </is>
       </c>
       <c r="C62" s="21">
-        <f>IF(C61&lt;=0,"nooit",C45/C61)</f>
+        <f>$C$8*C36</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>Restwaarde, accuvervanging, financieringskosten en ETS2 zitten hier NIET in — zie doc §6.5</t>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Diesel — reparaties</t>
+        </is>
+      </c>
+      <c r="C63" s="21">
+        <f>C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Diesel — motorrijtuigenbelasting</t>
+        </is>
+      </c>
+      <c r="C64" s="21">
+        <f>C37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Diesel totaal</t>
+        </is>
+      </c>
+      <c r="C65" s="22">
+        <f>SUM(C59:C64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — stroom</t>
+        </is>
+      </c>
+      <c r="C66" s="21">
+        <f>$C$8*C32*$C$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — vrachtwagenheffing</t>
+        </is>
+      </c>
+      <c r="C67" s="21">
+        <f>$C$8*$C$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — onderhoud</t>
+        </is>
+      </c>
+      <c r="C68" s="21">
+        <f>$C$8*C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — banden</t>
+        </is>
+      </c>
+      <c r="C69" s="21">
+        <f>$C$8*C36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — reparaties</t>
+        </is>
+      </c>
+      <c r="C70" s="21">
+        <f>C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — motorrijtuigenbelasting</t>
+        </is>
+      </c>
+      <c r="C71" s="21">
+        <f>C37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — extra chauffeurskosten</t>
+        </is>
+      </c>
+      <c r="C72" s="21">
+        <f>$C$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch totaal</t>
+        </is>
+      </c>
+      <c r="C73" s="22">
+        <f>SUM(C66:C72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Besparing per truck per jaar</t>
+        </is>
+      </c>
+      <c r="C74" s="21">
+        <f>C65-C73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Besparing alle trucks per jaar</t>
+        </is>
+      </c>
+      <c r="C75" s="22">
+        <f>C74*$C$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>6. UITKOMST</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Totale extra investering</t>
+        </is>
+      </c>
+      <c r="C78" s="21">
+        <f>C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Besparing per jaar</t>
+        </is>
+      </c>
+      <c r="C79" s="21">
+        <f>C75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>TERUGVERDIENTIJD (jaren)</t>
+        </is>
+      </c>
+      <c r="C80" s="24">
+        <f>IF(C79&lt;=0,"nooit",C56/C79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>Restwaarde staat aan beide kanten op nul. Accuvervanging, financieringskosten en ETS2 zitten er niet in.</t>
         </is>
       </c>
     </row>
@@ -1217,13 +1454,765 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E30"/>
+  <dimension ref="B1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Parameters overgenomen uit TCO-ZET-Vracht v7.3 (Panteia / Topsector Logistiek, 23-09-2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Basisjaar 2024. Blauw = letterlijk uit de tool, met broncel erbij.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>VOERTUIGTYPEN</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Voertuigtype</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Diesel [l/km]</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Elektrisch [kWh/km]</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>Onderhoud diesel [€/km]</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>Onderhoud elektrisch [€/km]</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Reparaties [€/jaar]</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="inlineStr">
+        <is>
+          <t>Banden [€/km]</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t>Wegenbelasting [€/jaar]</t>
+        </is>
+      </c>
+      <c r="J5" s="27" t="inlineStr">
+        <is>
+          <t>AanZET-categorie</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Kleine bakwagen</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>0.1323997619652777</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>0.4761551824999992</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>0.05729283728200001</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>0.02864641864100001</v>
+      </c>
+      <c r="G6" s="32" t="n">
+        <v>551.25</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>0.023121345</v>
+      </c>
+      <c r="I6" s="32" t="n">
+        <v>380</v>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Medium bakwagen</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>0.2106393949902324</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>0.9519194221532747</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>0.06302015160140001</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>0.0315100758007</v>
+      </c>
+      <c r="G7" s="32" t="n">
+        <v>551.25</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <v>0.0227691285</v>
+      </c>
+      <c r="I7" s="32" t="n">
+        <v>380</v>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>N3 Bakwagen (lvm &lt;= 18t)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Grote bakwagen</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>0.2697424784835717</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>1.327285842517089</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>0.06874746592080001</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>0.03437373296040001</v>
+      </c>
+      <c r="G8" s="32" t="n">
+        <v>1102.5</v>
+      </c>
+      <c r="H8" s="31" t="n">
+        <v>0.022416912</v>
+      </c>
+      <c r="I8" s="32" t="n">
+        <v>380</v>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>N3 Bakwagen (lvm &gt; 18t)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Lichte trekker z/opl</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>0.2794114755568611</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>1.299629854013712</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>0.0801939981012</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>0.0400969990506</v>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>1653.75</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>0.03444994</v>
+      </c>
+      <c r="I9" s="32" t="n">
+        <v>1028</v>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>N3 Trekker</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Zware trekker z/opl</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>0.3413502921361025</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>1.4675</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>0.09164053028160001</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>0.0458202651408</v>
+      </c>
+      <c r="G10" s="32" t="n">
+        <v>1653.75</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <v>0.04648296799999999</v>
+      </c>
+      <c r="I10" s="32" t="n">
+        <v>1028</v>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>N3 Trekker</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Bron: blad 'Invoer en categorieën', tabellen B21:K25 en B31:O35; categorie uit 'M2-Subsidie' F27:G31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>AANZET 2026 — PERCENTAGES EN MAXIMA</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>AanZET-categorie</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Ondernemingsgrootte</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Max. steun [%]</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>Max. steun [€]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>Middelgroot</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>Klein</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="F17" s="32" t="n">
+        <v>18800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>Groot</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="F18" s="32" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>N3 Bakwagen (lvm &lt;= 18t)</t>
+        </is>
+      </c>
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>Middelgroot</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F19" s="32" t="n">
+        <v>60500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>N3 Bakwagen (lvm &lt;= 18t)</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>Klein</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="F20" s="32" t="n">
+        <v>86600</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>N3 Bakwagen (lvm &lt;= 18t)</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>Groot</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>31100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>N3 Bakwagen (lvm &gt; 18t)</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>Middelgroot</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F22" s="32" t="n">
+        <v>83200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>N3 Bakwagen (lvm &gt; 18t)</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>Klein</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F23" s="32" t="n">
+        <v>115200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>N3 Bakwagen (lvm &gt; 18t)</t>
+        </is>
+      </c>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>Groot</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="F24" s="32" t="n">
+        <v>43900</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>N3 Trekker</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>Middelgroot</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F25" s="32" t="n">
+        <v>83200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>N3 Trekker</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>Klein</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F26" s="32" t="n">
+        <v>115200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>N3 Trekker</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>Groot</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="F27" s="32" t="n">
+        <v>43900</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Bron: blad 'M2-Subsidie' F5:I17. Komt exact overeen met de bedragen die RVO en de dealers publiceren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>STAATSSTEUNPLAFOND — MAXIMALE STEUN ALS % VAN DE MEERPRIJS</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>Groot</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t>Middelgroot</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>Klein</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Bron: blad 'M2-Subsidie' F21:G23. Werkt als derde plafond naast percentage en maximumbedrag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>ENERGIE- EN FINANCIELE PARAMETERS</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Kale dieselprijs [€/l]</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Parameters D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Accijns diesel [€/l]</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>0.5163</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Parameters D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Inkoopprijs netstroom [€/kWh]</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>0.21537</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Parameters D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Prijs eigen opwek [€/kWh]</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Parameters J47</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Fractie eigen opwek</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Parameters J46</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Rente</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Parameters D30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Verzekering (% van bruto aanschaf)</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="n">
+        <v>0.03568675887</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Parameters D31</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Restwaarde na 7 jaar</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Parameters I21</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Economische levensduur [jaar]</t>
+        </is>
+      </c>
+      <c r="D46" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Input-Output Module D36</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Jaarlijkse stijging dieselprijs</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Parameters I31</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Jaarlijkse stijging energiekosten</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Parameters I32</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1235,9 +2224,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Rekent live mee met de invoer op het blad Model. Alleen de eerste kolom is invoer.</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Rekent live mee met blad Model. Alleen de eerste kolom is invoer.</t>
         </is>
       </c>
     </row>
@@ -1252,19 +2241,19 @@
       <c r="E4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>km per truck per jaar</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>km per jaar</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>Besparing per jaar</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Terugverdientijd (jaren)</t>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>Terugverdientijd [jaar]</t>
         </is>
       </c>
     </row>
@@ -1272,12 +2261,12 @@
       <c r="B6" s="7" t="n">
         <v>60000</v>
       </c>
-      <c r="C6" s="19">
-        <f>B6*((Model!$C$12/100*Model!$C$13+Model!$C$18+Model!$C$16)-(Model!$C$14*Model!$C$15+Model!$C$19+Model!$C$17))*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D6" s="22">
-        <f>IF(C6&lt;=0,"nooit",Model!$C$45/C6)</f>
+      <c r="C6" s="21">
+        <f>(B6*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D6" s="37">
+        <f>IF(C6&lt;=0,"nooit",Model!$C$56/C6)</f>
         <v/>
       </c>
     </row>
@@ -1285,12 +2274,12 @@
       <c r="B7" s="7" t="n">
         <v>80000</v>
       </c>
-      <c r="C7" s="19">
-        <f>B7*((Model!$C$12/100*Model!$C$13+Model!$C$18+Model!$C$16)-(Model!$C$14*Model!$C$15+Model!$C$19+Model!$C$17))*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D7" s="22">
-        <f>IF(C7&lt;=0,"nooit",Model!$C$45/C7)</f>
+      <c r="C7" s="21">
+        <f>(B7*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D7" s="37">
+        <f>IF(C7&lt;=0,"nooit",Model!$C$56/C7)</f>
         <v/>
       </c>
     </row>
@@ -1298,12 +2287,12 @@
       <c r="B8" s="7" t="n">
         <v>100000</v>
       </c>
-      <c r="C8" s="19">
-        <f>B8*((Model!$C$12/100*Model!$C$13+Model!$C$18+Model!$C$16)-(Model!$C$14*Model!$C$15+Model!$C$19+Model!$C$17))*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D8" s="22">
-        <f>IF(C8&lt;=0,"nooit",Model!$C$45/C8)</f>
+      <c r="C8" s="21">
+        <f>(B8*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D8" s="37">
+        <f>IF(C8&lt;=0,"nooit",Model!$C$56/C8)</f>
         <v/>
       </c>
     </row>
@@ -1311,12 +2300,12 @@
       <c r="B9" s="7" t="n">
         <v>120000</v>
       </c>
-      <c r="C9" s="19">
-        <f>B9*((Model!$C$12/100*Model!$C$13+Model!$C$18+Model!$C$16)-(Model!$C$14*Model!$C$15+Model!$C$19+Model!$C$17))*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D9" s="22">
-        <f>IF(C9&lt;=0,"nooit",Model!$C$45/C9)</f>
+      <c r="C9" s="21">
+        <f>(B9*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D9" s="37">
+        <f>IF(C9&lt;=0,"nooit",Model!$C$56/C9)</f>
         <v/>
       </c>
     </row>
@@ -1324,12 +2313,12 @@
       <c r="B10" s="7" t="n">
         <v>150000</v>
       </c>
-      <c r="C10" s="19">
-        <f>B10*((Model!$C$12/100*Model!$C$13+Model!$C$18+Model!$C$16)-(Model!$C$14*Model!$C$15+Model!$C$19+Model!$C$17))*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D10" s="22">
-        <f>IF(C10&lt;=0,"nooit",Model!$C$45/C10)</f>
+      <c r="C10" s="21">
+        <f>(B10*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D10" s="37">
+        <f>IF(C10&lt;=0,"nooit",Model!$C$56/C10)</f>
         <v/>
       </c>
     </row>
@@ -1337,12 +2326,12 @@
       <c r="B11" s="7" t="n">
         <v>180000</v>
       </c>
-      <c r="C11" s="19">
-        <f>B11*((Model!$C$12/100*Model!$C$13+Model!$C$18+Model!$C$16)-(Model!$C$14*Model!$C$15+Model!$C$19+Model!$C$17))*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D11" s="22">
-        <f>IF(C11&lt;=0,"nooit",Model!$C$45/C11)</f>
+      <c r="C11" s="21">
+        <f>(B11*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D11" s="37">
+        <f>IF(C11&lt;=0,"nooit",Model!$C$56/C11)</f>
         <v/>
       </c>
     </row>
@@ -1350,19 +2339,19 @@
       <c r="B12" s="7" t="n">
         <v>200000</v>
       </c>
-      <c r="C12" s="19">
-        <f>B12*((Model!$C$12/100*Model!$C$13+Model!$C$18+Model!$C$16)-(Model!$C$14*Model!$C$15+Model!$C$19+Model!$C$17))*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D12" s="22">
-        <f>IF(C12&lt;=0,"nooit",Model!$C$45/C12)</f>
+      <c r="C12" s="21">
+        <f>(B12*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D12" s="37">
+        <f>IF(C12&lt;=0,"nooit",Model!$C$56/C12)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>B. STROOMPRIJS ALL-IN</t>
+          <t>B. GEMENGDE STROOMPRIJS</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -1370,32 +2359,32 @@
       <c r="E15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>€ per kWh</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>Besparing per jaar</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Terugverdientijd (jaren)</t>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Terugverdientijd [jaar]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C17" s="19">
-        <f>Model!$C$57+(Model!$C$15-B17)*Model!$C$8*Model!$C$14*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D17" s="22">
-        <f>IF(C17&lt;=0,"nooit",Model!$C$45/C17)</f>
+        <v>0.11</v>
+      </c>
+      <c r="C17" s="21">
+        <f>Model!$C$75+(Model!$C$19-B17)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D17" s="37">
+        <f>IF(C17&lt;=0,"nooit",Model!$C$56/C17)</f>
         <v/>
       </c>
     </row>
@@ -1403,84 +2392,84 @@
       <c r="B18" s="12" t="n">
         <v>0.14</v>
       </c>
-      <c r="C18" s="19">
-        <f>Model!$C$57+(Model!$C$15-B18)*Model!$C$8*Model!$C$14*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D18" s="22">
-        <f>IF(C18&lt;=0,"nooit",Model!$C$45/C18)</f>
+      <c r="C18" s="21">
+        <f>Model!$C$75+(Model!$C$19-B18)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D18" s="37">
+        <f>IF(C18&lt;=0,"nooit",Model!$C$56/C18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C19" s="19">
-        <f>Model!$C$57+(Model!$C$15-B19)*Model!$C$8*Model!$C$14*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D19" s="22">
-        <f>IF(C19&lt;=0,"nooit",Model!$C$45/C19)</f>
+        <v>0.16</v>
+      </c>
+      <c r="C19" s="21">
+        <f>Model!$C$75+(Model!$C$19-B19)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D19" s="37">
+        <f>IF(C19&lt;=0,"nooit",Model!$C$56/C19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C20" s="19">
-        <f>Model!$C$57+(Model!$C$15-B20)*Model!$C$8*Model!$C$14*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D20" s="22">
-        <f>IF(C20&lt;=0,"nooit",Model!$C$45/C20)</f>
+        <v>0.18</v>
+      </c>
+      <c r="C20" s="21">
+        <f>Model!$C$75+(Model!$C$19-B20)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D20" s="37">
+        <f>IF(C20&lt;=0,"nooit",Model!$C$56/C20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="C21" s="19">
-        <f>Model!$C$57+(Model!$C$15-B21)*Model!$C$8*Model!$C$14*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D21" s="22">
-        <f>IF(C21&lt;=0,"nooit",Model!$C$45/C21)</f>
+        <v>0.2154</v>
+      </c>
+      <c r="C21" s="21">
+        <f>Model!$C$75+(Model!$C$19-B21)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D21" s="37">
+        <f>IF(C21&lt;=0,"nooit",Model!$C$56/C21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C22" s="19">
-        <f>Model!$C$57+(Model!$C$15-B22)*Model!$C$8*Model!$C$14*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D22" s="22">
-        <f>IF(C22&lt;=0,"nooit",Model!$C$45/C22)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C22" s="21">
+        <f>Model!$C$75+(Model!$C$19-B22)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D22" s="37">
+        <f>IF(C22&lt;=0,"nooit",Model!$C$56/C22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C23" s="19">
-        <f>Model!$C$57+(Model!$C$15-B23)*Model!$C$8*Model!$C$14*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D23" s="22">
-        <f>IF(C23&lt;=0,"nooit",Model!$C$45/C23)</f>
+        <v>0.3</v>
+      </c>
+      <c r="C23" s="21">
+        <f>Model!$C$75+(Model!$C$19-B23)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D23" s="37">
+        <f>IF(C23&lt;=0,"nooit",Model!$C$56/C23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>C. ONDERNEMINGSGROOTTE — WAT DE MKB-TOETS WAARD IS</t>
+          <t>C. DIESELVERBRUIK — 1 OP ...</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -1488,78 +2477,200 @@
       <c r="E26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>1 op ...</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>Besparing per jaar</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>Terugverdientijd [jaar]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C28" s="21">
+        <f>Model!$C$75+(1/B28-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D28" s="37">
+        <f>IF(C28&lt;=0,"nooit",Model!$C$56/C28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C29" s="21">
+        <f>Model!$C$75+(1/B29-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D29" s="37">
+        <f>IF(C29&lt;=0,"nooit",Model!$C$56/C29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C30" s="21">
+        <f>Model!$C$75+(1/B30-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D30" s="37">
+        <f>IF(C30&lt;=0,"nooit",Model!$C$56/C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C31" s="21">
+        <f>Model!$C$75+(1/B31-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D31" s="37">
+        <f>IF(C31&lt;=0,"nooit",Model!$C$56/C31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C32" s="21">
+        <f>Model!$C$75+(1/B32-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D32" s="37">
+        <f>IF(C32&lt;=0,"nooit",Model!$C$56/C32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C33" s="21">
+        <f>Model!$C$75+(1/B33-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D33" s="37">
+        <f>IF(C33&lt;=0,"nooit",Model!$C$56/C33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="21">
+        <f>Model!$C$75+(1/B34-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D34" s="37">
+        <f>IF(C34&lt;=0,"nooit",Model!$C$56/C34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>D. ONDERNEMINGSGROOTTE</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>Grootte</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C38" s="33" t="inlineStr">
         <is>
           <t>AanZET totaal</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D38" s="33" t="inlineStr">
         <is>
           <t>Extra investering</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Terugverdientijd (jaren)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="6">
-        <f>Model!$B$27</f>
-        <v/>
-      </c>
-      <c r="C28" s="19">
-        <f>MIN(Model!$C$10*Model!$C$27,Model!$D$27)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D28" s="19">
-        <f>(Model!$C$39-MIN(Model!$C$10*Model!$C$27,Model!$D$27)-MAX(0,Model!$C$39-MIN(Model!$C$10*Model!$C$27,Model!$D$27))*Model!$C$21*Model!$C$20)*Model!$C$7+Model!$C$44</f>
-        <v/>
-      </c>
-      <c r="E28" s="22">
-        <f>IF(Model!$C$57&lt;=0,"nooit",D28/Model!$C$57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="6">
-        <f>Model!$B$28</f>
-        <v/>
-      </c>
-      <c r="C29" s="19">
-        <f>MIN(Model!$C$10*Model!$C$28,Model!$D$28)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D29" s="19">
-        <f>(Model!$C$39-MIN(Model!$C$10*Model!$C$28,Model!$D$28)-MAX(0,Model!$C$39-MIN(Model!$C$10*Model!$C$28,Model!$D$28))*Model!$C$21*Model!$C$20)*Model!$C$7+Model!$C$44</f>
-        <v/>
-      </c>
-      <c r="E29" s="22">
-        <f>IF(Model!$C$57&lt;=0,"nooit",D29/Model!$C$57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="6">
-        <f>Model!$B$29</f>
-        <v/>
-      </c>
-      <c r="C30" s="19">
-        <f>MIN(Model!$C$10*Model!$C$29,Model!$D$29)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D30" s="19">
-        <f>(Model!$C$39-MIN(Model!$C$10*Model!$C$29,Model!$D$29)-MAX(0,Model!$C$39-MIN(Model!$C$10*Model!$C$29,Model!$D$29))*Model!$C$21*Model!$C$20)*Model!$C$7+Model!$C$44</f>
-        <v/>
-      </c>
-      <c r="E30" s="22">
-        <f>IF(Model!$C$57&lt;=0,"nooit",D30/Model!$C$57)</f>
+      <c r="E38" s="33" t="inlineStr">
+        <is>
+          <t>Terugverdientijd [jaar]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Klein</t>
+        </is>
+      </c>
+      <c r="C39" s="21">
+        <f>MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B39,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D39" s="21">
+        <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B39,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B39,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
+        <v/>
+      </c>
+      <c r="E39" s="37">
+        <f>IF(Model!$C$75&lt;=0,"nooit",D39/Model!$C$75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Middelgroot</t>
+        </is>
+      </c>
+      <c r="C40" s="21">
+        <f>MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B40,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D40" s="21">
+        <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B40,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B40,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
+        <v/>
+      </c>
+      <c r="E40" s="37">
+        <f>IF(Model!$C$75&lt;=0,"nooit",D40/Model!$C$75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Groot</t>
+        </is>
+      </c>
+      <c r="C41" s="21">
+        <f>MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B41,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D41" s="21">
+        <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B41,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B41,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
+        <v/>
+      </c>
+      <c r="E41" s="37">
+        <f>IF(Model!$C$75&lt;=0,"nooit",D41/Model!$C$75)</f>
         <v/>
       </c>
     </row>

--- a/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
+++ b/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>1.6063</v>
+        <v>1.7</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>

--- a/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
+++ b/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>280000</v>
+        <v>300000</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>120000</v>
+        <v>146166</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>

--- a/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
+++ b/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="€#,##0.00;(€#,##0.00);-"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,11 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -121,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,8 +152,10 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -527,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G81"/>
+  <dimension ref="B1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -596,7 +603,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>VERVANGEN door werkelijk jaarkilometrage — grootste hefboom in het model</t>
+          <t>Opgave Kwekerij Baas</t>
         </is>
       </c>
     </row>
@@ -671,7 +678,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>AANNAME — opvragen bij de dealer. Grondslag voor AanZET</t>
+          <t>Opgave Nijwa: Volvo FH Aero Electric 4x2. De 6x2 kost € 320.000</t>
         </is>
       </c>
     </row>
@@ -686,7 +693,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>AANNAME. Bepaalt de meerprijs en daarmee het staatssteunplafond</t>
+          <t>Panteia casco 'Zware trekker z/opl'. OPVRAGEN bij Nijwa — bepaalt het staatssteunplafond</t>
         </is>
       </c>
     </row>
@@ -701,7 +708,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Panteia Parameters D4+D5: kale prijs €1.09 + accijns €0.5163</t>
+          <t>Opgave Kwekerij Baas</t>
         </is>
       </c>
     </row>
@@ -716,7 +723,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Panteia Parameters J46</t>
+          <t>Opgave Kwekerij Baas — volledig eigen opwek</t>
         </is>
       </c>
     </row>
@@ -731,7 +738,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Panteia Parameters J47</t>
+          <t>Opgave Kwekerij Baas</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1401,7 @@
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>6. UITKOMST</t>
+          <t>6. UITKOMST ZONDER ERE</t>
         </is>
       </c>
       <c r="C77" s="5" t="n"/>
@@ -1428,7 +1435,7 @@
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>TERUGVERDIENTIJD (jaren)</t>
+          <t>Terugverdientijd (jaren)</t>
         </is>
       </c>
       <c r="C80" s="24">
@@ -1436,8 +1443,117 @@
         <v/>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="25" t="inlineStr">
+    <row r="82">
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>7. ERE — EMISSIEREDUCTIE-EENHEDEN</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Geladen kWh per jaar (beide trucks)</t>
+        </is>
+      </c>
+      <c r="C83" s="25">
+        <f>$C$8*C32*$C$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>ERE-waarde per geladen kWh</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Bandbreedte € 0,07 - € 0,14; circa € 0,10 in 2026. Aantoonbaar hernieuwbaar levert de bovenkant op</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Commissie inboekdienstverlener</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>AANNAME — opvragen. Inboeken kan alleen via een dienstverlener, tenzij je zelf &gt; 2 mln kWh per jaar laadt</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Bruto ERE-opbrengst per jaar</t>
+        </is>
+      </c>
+      <c r="C86" s="21">
+        <f>C83*C84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Netto ERE-opbrengst per jaar</t>
+        </is>
+      </c>
+      <c r="C87" s="22">
+        <f>C86*(1-C85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>8. UITKOMST MET ERE</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Besparing per jaar inclusief ERE</t>
+        </is>
+      </c>
+      <c r="C90" s="21">
+        <f>C75+C87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>TERUGVERDIENTIJD (jaren)</t>
+        </is>
+      </c>
+      <c r="C91" s="26">
+        <f>IF(C90&lt;=0,"nooit",C56/C90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>Restwaarde staat aan beide kanten op nul. Accuvervanging, financieringskosten en ETS2 zitten er niet in.</t>
         </is>
@@ -1470,7 +1586,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>Parameters overgenomen uit TCO-ZET-Vracht v7.3 (Panteia / Topsector Logistiek, 23-09-2024)</t>
         </is>
@@ -1499,212 +1615,212 @@
       <c r="J4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Voertuigtype</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Diesel [l/km]</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>Elektrisch [kWh/km]</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Onderhoud diesel [€/km]</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>Onderhoud elektrisch [€/km]</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>Reparaties [€/jaar]</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>Banden [€/km]</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>Wegenbelasting [€/jaar]</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="29" t="inlineStr">
         <is>
           <t>AanZET-categorie</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Kleine bakwagen</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="31" t="n">
         <v>0.1323997619652777</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="32" t="n">
         <v>0.4761551824999992</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="33" t="n">
         <v>0.05729283728200001</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="33" t="n">
         <v>0.02864641864100001</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="34" t="n">
         <v>551.25</v>
       </c>
-      <c r="H6" s="31" t="n">
+      <c r="H6" s="33" t="n">
         <v>0.023121345</v>
       </c>
-      <c r="I6" s="32" t="n">
+      <c r="I6" s="34" t="n">
         <v>380</v>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="30" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Medium bakwagen</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="31" t="n">
         <v>0.2106393949902324</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="32" t="n">
         <v>0.9519194221532747</v>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="E7" s="33" t="n">
         <v>0.06302015160140001</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="33" t="n">
         <v>0.0315100758007</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="34" t="n">
         <v>551.25</v>
       </c>
-      <c r="H7" s="31" t="n">
+      <c r="H7" s="33" t="n">
         <v>0.0227691285</v>
       </c>
-      <c r="I7" s="32" t="n">
+      <c r="I7" s="34" t="n">
         <v>380</v>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="30" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &lt;= 18t)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Grote bakwagen</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="31" t="n">
         <v>0.2697424784835717</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="32" t="n">
         <v>1.327285842517089</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="33" t="n">
         <v>0.06874746592080001</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="33" t="n">
         <v>0.03437373296040001</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="34" t="n">
         <v>1102.5</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="33" t="n">
         <v>0.022416912</v>
       </c>
-      <c r="I8" s="32" t="n">
+      <c r="I8" s="34" t="n">
         <v>380</v>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="30" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &gt; 18t)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Lichte trekker z/opl</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="31" t="n">
         <v>0.2794114755568611</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="32" t="n">
         <v>1.299629854013712</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="33" t="n">
         <v>0.0801939981012</v>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="F9" s="33" t="n">
         <v>0.0400969990506</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="34" t="n">
         <v>1653.75</v>
       </c>
-      <c r="H9" s="31" t="n">
+      <c r="H9" s="33" t="n">
         <v>0.03444994</v>
       </c>
-      <c r="I9" s="32" t="n">
+      <c r="I9" s="34" t="n">
         <v>1028</v>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="30" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Zware trekker z/opl</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="31" t="n">
         <v>0.3413502921361025</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="32" t="n">
         <v>1.4675</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="33" t="n">
         <v>0.09164053028160001</v>
       </c>
-      <c r="F10" s="31" t="n">
+      <c r="F10" s="33" t="n">
         <v>0.0458202651408</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="34" t="n">
         <v>1653.75</v>
       </c>
-      <c r="H10" s="31" t="n">
+      <c r="H10" s="33" t="n">
         <v>0.04648296799999999</v>
       </c>
-      <c r="I10" s="32" t="n">
+      <c r="I10" s="34" t="n">
         <v>1028</v>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="30" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
@@ -1729,240 +1845,240 @@
       <c r="F14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>AanZET-categorie</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>Ondernemingsgrootte</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>Max. steun [%]</t>
         </is>
       </c>
-      <c r="F15" s="33" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>Max. steun [€]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="37" t="n">
         <v>0.12</v>
       </c>
-      <c r="F16" s="32" t="n">
+      <c r="F16" s="34" t="n">
         <v>14700</v>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="37" t="n">
         <v>0.148</v>
       </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="34" t="n">
         <v>18800</v>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="37" t="n">
         <v>0.061</v>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="34" t="n">
         <v>7500</v>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &lt;= 18t)</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="37" t="n">
         <v>0.2</v>
       </c>
-      <c r="F19" s="32" t="n">
+      <c r="F19" s="34" t="n">
         <v>60500</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &lt;= 18t)</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="37" t="n">
         <v>0.286</v>
       </c>
-      <c r="F20" s="32" t="n">
+      <c r="F20" s="34" t="n">
         <v>86600</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &lt;= 18t)</t>
         </is>
       </c>
-      <c r="D21" s="34" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="37" t="n">
         <v>0.103</v>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F21" s="34" t="n">
         <v>31100</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &gt; 18t)</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E22" s="35" t="n">
+      <c r="E22" s="37" t="n">
         <v>0.21</v>
       </c>
-      <c r="F22" s="32" t="n">
+      <c r="F22" s="34" t="n">
         <v>83200</v>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &gt; 18t)</t>
         </is>
       </c>
-      <c r="D23" s="34" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="E23" s="35" t="n">
+      <c r="E23" s="37" t="n">
         <v>0.29</v>
       </c>
-      <c r="F23" s="32" t="n">
+      <c r="F23" s="34" t="n">
         <v>115200</v>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &gt; 18t)</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="E24" s="35" t="n">
+      <c r="E24" s="37" t="n">
         <v>0.111</v>
       </c>
-      <c r="F24" s="32" t="n">
+      <c r="F24" s="34" t="n">
         <v>43900</v>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
       </c>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E25" s="35" t="n">
+      <c r="E25" s="37" t="n">
         <v>0.21</v>
       </c>
-      <c r="F25" s="32" t="n">
+      <c r="F25" s="34" t="n">
         <v>83200</v>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="E26" s="35" t="n">
+      <c r="E26" s="37" t="n">
         <v>0.29</v>
       </c>
-      <c r="F26" s="32" t="n">
+      <c r="F26" s="34" t="n">
         <v>115200</v>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="E27" s="35" t="n">
+      <c r="E27" s="37" t="n">
         <v>0.111</v>
       </c>
-      <c r="F27" s="32" t="n">
+      <c r="F27" s="34" t="n">
         <v>43900</v>
       </c>
     </row>
@@ -1984,32 +2100,32 @@
       <c r="E30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="37" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="34" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="D32" s="35" t="n">
+      <c r="D32" s="37" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="D33" s="35" t="n">
+      <c r="D33" s="37" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2036,7 +2152,7 @@
           <t>Kale dieselprijs [€/l]</t>
         </is>
       </c>
-      <c r="D38" s="31" t="n">
+      <c r="D38" s="33" t="n">
         <v>1.09</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2051,7 +2167,7 @@
           <t>Accijns diesel [€/l]</t>
         </is>
       </c>
-      <c r="D39" s="31" t="n">
+      <c r="D39" s="33" t="n">
         <v>0.5163</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2066,7 +2182,7 @@
           <t>Inkoopprijs netstroom [€/kWh]</t>
         </is>
       </c>
-      <c r="D40" s="31" t="n">
+      <c r="D40" s="33" t="n">
         <v>0.21537</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2081,7 +2197,7 @@
           <t>Prijs eigen opwek [€/kWh]</t>
         </is>
       </c>
-      <c r="D41" s="31" t="n">
+      <c r="D41" s="33" t="n">
         <v>0.11</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2096,7 +2212,7 @@
           <t>Fractie eigen opwek</t>
         </is>
       </c>
-      <c r="D42" s="35" t="n">
+      <c r="D42" s="37" t="n">
         <v>0.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2111,7 +2227,7 @@
           <t>Rente</t>
         </is>
       </c>
-      <c r="D43" s="35" t="n">
+      <c r="D43" s="37" t="n">
         <v>0.039</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2126,7 +2242,7 @@
           <t>Verzekering (% van bruto aanschaf)</t>
         </is>
       </c>
-      <c r="D44" s="35" t="n">
+      <c r="D44" s="37" t="n">
         <v>0.03568675887</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2141,7 +2257,7 @@
           <t>Restwaarde na 7 jaar</t>
         </is>
       </c>
-      <c r="D45" s="35" t="n">
+      <c r="D45" s="37" t="n">
         <v>0.23</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2156,7 +2272,7 @@
           <t>Economische levensduur [jaar]</t>
         </is>
       </c>
-      <c r="D46" s="36" t="n">
+      <c r="D46" s="38" t="n">
         <v>7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2171,7 +2287,7 @@
           <t>Jaarlijkse stijging dieselprijs</t>
         </is>
       </c>
-      <c r="D47" s="35" t="n">
+      <c r="D47" s="37" t="n">
         <v>0.01</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2186,7 +2302,7 @@
           <t>Jaarlijkse stijging energiekosten</t>
         </is>
       </c>
-      <c r="D48" s="35" t="n">
+      <c r="D48" s="37" t="n">
         <v>0.01</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2241,17 +2357,17 @@
       <c r="E4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>km per jaar</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Besparing per jaar</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Terugverdientijd [jaar]</t>
         </is>
@@ -2262,10 +2378,10 @@
         <v>60000</v>
       </c>
       <c r="C6" s="21">
-        <f>(B6*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D6" s="37">
+        <f>(B6*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B6*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <v/>
+      </c>
+      <c r="D6" s="39">
         <f>IF(C6&lt;=0,"nooit",Model!$C$56/C6)</f>
         <v/>
       </c>
@@ -2275,10 +2391,10 @@
         <v>80000</v>
       </c>
       <c r="C7" s="21">
-        <f>(B7*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D7" s="37">
+        <f>(B7*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B7*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <v/>
+      </c>
+      <c r="D7" s="39">
         <f>IF(C7&lt;=0,"nooit",Model!$C$56/C7)</f>
         <v/>
       </c>
@@ -2288,10 +2404,10 @@
         <v>100000</v>
       </c>
       <c r="C8" s="21">
-        <f>(B8*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D8" s="37">
+        <f>(B8*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B8*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <v/>
+      </c>
+      <c r="D8" s="39">
         <f>IF(C8&lt;=0,"nooit",Model!$C$56/C8)</f>
         <v/>
       </c>
@@ -2301,10 +2417,10 @@
         <v>120000</v>
       </c>
       <c r="C9" s="21">
-        <f>(B9*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D9" s="37">
+        <f>(B9*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B9*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <v/>
+      </c>
+      <c r="D9" s="39">
         <f>IF(C9&lt;=0,"nooit",Model!$C$56/C9)</f>
         <v/>
       </c>
@@ -2314,10 +2430,10 @@
         <v>150000</v>
       </c>
       <c r="C10" s="21">
-        <f>(B10*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D10" s="37">
+        <f>(B10*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B10*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <v/>
+      </c>
+      <c r="D10" s="39">
         <f>IF(C10&lt;=0,"nooit",Model!$C$56/C10)</f>
         <v/>
       </c>
@@ -2327,10 +2443,10 @@
         <v>180000</v>
       </c>
       <c r="C11" s="21">
-        <f>(B11*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D11" s="37">
+        <f>(B11*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B11*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <v/>
+      </c>
+      <c r="D11" s="39">
         <f>IF(C11&lt;=0,"nooit",Model!$C$56/C11)</f>
         <v/>
       </c>
@@ -2340,10 +2456,10 @@
         <v>200000</v>
       </c>
       <c r="C12" s="21">
-        <f>(B12*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D12" s="37">
+        <f>(B12*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B12*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <v/>
+      </c>
+      <c r="D12" s="39">
         <f>IF(C12&lt;=0,"nooit",Model!$C$56/C12)</f>
         <v/>
       </c>
@@ -2359,17 +2475,17 @@
       <c r="E15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>€ per kWh</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Besparing per jaar</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>Terugverdientijd [jaar]</t>
         </is>
@@ -2380,10 +2496,10 @@
         <v>0.11</v>
       </c>
       <c r="C17" s="21">
-        <f>Model!$C$75+(Model!$C$19-B17)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D17" s="37">
+        <f>Model!$C$90+(Model!$C$19-B17)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D17" s="39">
         <f>IF(C17&lt;=0,"nooit",Model!$C$56/C17)</f>
         <v/>
       </c>
@@ -2393,10 +2509,10 @@
         <v>0.14</v>
       </c>
       <c r="C18" s="21">
-        <f>Model!$C$75+(Model!$C$19-B18)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D18" s="37">
+        <f>Model!$C$90+(Model!$C$19-B18)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D18" s="39">
         <f>IF(C18&lt;=0,"nooit",Model!$C$56/C18)</f>
         <v/>
       </c>
@@ -2406,10 +2522,10 @@
         <v>0.16</v>
       </c>
       <c r="C19" s="21">
-        <f>Model!$C$75+(Model!$C$19-B19)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D19" s="37">
+        <f>Model!$C$90+(Model!$C$19-B19)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D19" s="39">
         <f>IF(C19&lt;=0,"nooit",Model!$C$56/C19)</f>
         <v/>
       </c>
@@ -2419,10 +2535,10 @@
         <v>0.18</v>
       </c>
       <c r="C20" s="21">
-        <f>Model!$C$75+(Model!$C$19-B20)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D20" s="37">
+        <f>Model!$C$90+(Model!$C$19-B20)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D20" s="39">
         <f>IF(C20&lt;=0,"nooit",Model!$C$56/C20)</f>
         <v/>
       </c>
@@ -2432,10 +2548,10 @@
         <v>0.2154</v>
       </c>
       <c r="C21" s="21">
-        <f>Model!$C$75+(Model!$C$19-B21)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D21" s="37">
+        <f>Model!$C$90+(Model!$C$19-B21)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D21" s="39">
         <f>IF(C21&lt;=0,"nooit",Model!$C$56/C21)</f>
         <v/>
       </c>
@@ -2445,10 +2561,10 @@
         <v>0.25</v>
       </c>
       <c r="C22" s="21">
-        <f>Model!$C$75+(Model!$C$19-B22)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D22" s="37">
+        <f>Model!$C$90+(Model!$C$19-B22)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D22" s="39">
         <f>IF(C22&lt;=0,"nooit",Model!$C$56/C22)</f>
         <v/>
       </c>
@@ -2458,10 +2574,10 @@
         <v>0.3</v>
       </c>
       <c r="C23" s="21">
-        <f>Model!$C$75+(Model!$C$19-B23)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D23" s="37">
+        <f>Model!$C$90+(Model!$C$19-B23)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D23" s="39">
         <f>IF(C23&lt;=0,"nooit",Model!$C$56/C23)</f>
         <v/>
       </c>
@@ -2477,17 +2593,17 @@
       <c r="E26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>1 op ...</t>
         </is>
       </c>
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>Besparing per jaar</t>
         </is>
       </c>
-      <c r="D27" s="33" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>Terugverdientijd [jaar]</t>
         </is>
@@ -2498,10 +2614,10 @@
         <v>2.9</v>
       </c>
       <c r="C28" s="21">
-        <f>Model!$C$75+(1/B28-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D28" s="37">
+        <f>Model!$C$90+(1/B28-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D28" s="39">
         <f>IF(C28&lt;=0,"nooit",Model!$C$56/C28)</f>
         <v/>
       </c>
@@ -2511,10 +2627,10 @@
         <v>3.2</v>
       </c>
       <c r="C29" s="21">
-        <f>Model!$C$75+(1/B29-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D29" s="37">
+        <f>Model!$C$90+(1/B29-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D29" s="39">
         <f>IF(C29&lt;=0,"nooit",Model!$C$56/C29)</f>
         <v/>
       </c>
@@ -2524,10 +2640,10 @@
         <v>3.5</v>
       </c>
       <c r="C30" s="21">
-        <f>Model!$C$75+(1/B30-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D30" s="37">
+        <f>Model!$C$90+(1/B30-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D30" s="39">
         <f>IF(C30&lt;=0,"nooit",Model!$C$56/C30)</f>
         <v/>
       </c>
@@ -2537,10 +2653,10 @@
         <v>3.8</v>
       </c>
       <c r="C31" s="21">
-        <f>Model!$C$75+(1/B31-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D31" s="37">
+        <f>Model!$C$90+(1/B31-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D31" s="39">
         <f>IF(C31&lt;=0,"nooit",Model!$C$56/C31)</f>
         <v/>
       </c>
@@ -2550,10 +2666,10 @@
         <v>4.1</v>
       </c>
       <c r="C32" s="21">
-        <f>Model!$C$75+(1/B32-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D32" s="37">
+        <f>Model!$C$90+(1/B32-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D32" s="39">
         <f>IF(C32&lt;=0,"nooit",Model!$C$56/C32)</f>
         <v/>
       </c>
@@ -2563,10 +2679,10 @@
         <v>4.5</v>
       </c>
       <c r="C33" s="21">
-        <f>Model!$C$75+(1/B33-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D33" s="37">
+        <f>Model!$C$90+(1/B33-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D33" s="39">
         <f>IF(C33&lt;=0,"nooit",Model!$C$56/C33)</f>
         <v/>
       </c>
@@ -2576,10 +2692,10 @@
         <v>5</v>
       </c>
       <c r="C34" s="21">
-        <f>Model!$C$75+(1/B34-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D34" s="37">
+        <f>Model!$C$90+(1/B34-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D34" s="39">
         <f>IF(C34&lt;=0,"nooit",Model!$C$56/C34)</f>
         <v/>
       </c>
@@ -2596,22 +2712,22 @@
       <c r="F37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="33" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>Grootte</t>
         </is>
       </c>
-      <c r="C38" s="33" t="inlineStr">
+      <c r="C38" s="35" t="inlineStr">
         <is>
           <t>AanZET totaal</t>
         </is>
       </c>
-      <c r="D38" s="33" t="inlineStr">
+      <c r="D38" s="35" t="inlineStr">
         <is>
           <t>Extra investering</t>
         </is>
       </c>
-      <c r="E38" s="33" t="inlineStr">
+      <c r="E38" s="35" t="inlineStr">
         <is>
           <t>Terugverdientijd [jaar]</t>
         </is>
@@ -2631,8 +2747,8 @@
         <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B39,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B39,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
         <v/>
       </c>
-      <c r="E39" s="37">
-        <f>IF(Model!$C$75&lt;=0,"nooit",D39/Model!$C$75)</f>
+      <c r="E39" s="39">
+        <f>IF(Model!$C$90&lt;=0,"nooit",D39/Model!$C$90)</f>
         <v/>
       </c>
     </row>
@@ -2650,8 +2766,8 @@
         <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B40,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B40,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
         <v/>
       </c>
-      <c r="E40" s="37">
-        <f>IF(Model!$C$75&lt;=0,"nooit",D40/Model!$C$75)</f>
+      <c r="E40" s="39">
+        <f>IF(Model!$C$90&lt;=0,"nooit",D40/Model!$C$90)</f>
         <v/>
       </c>
     </row>
@@ -2669,8 +2785,8 @@
         <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B41,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B41,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
         <v/>
       </c>
-      <c r="E41" s="37">
-        <f>IF(Model!$C$75&lt;=0,"nooit",D41/Model!$C$75)</f>
+      <c r="E41" s="39">
+        <f>IF(Model!$C$90&lt;=0,"nooit",D41/Model!$C$90)</f>
         <v/>
       </c>
     </row>

--- a/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
+++ b/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
@@ -1570,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J48"/>
+  <dimension ref="B1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1583,6 +1583,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="90" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1803,7 +1804,7 @@
         <v>0.3413502921361025</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>1.4675</v>
+        <v>1.155</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>0.09164053028160001</v>
@@ -1823,6 +1824,11 @@
       <c r="J10" s="30" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
+        </is>
+      </c>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t>VERVANGEN — Volvo ERS 18-08-2026, route Ens-Naaldwijk: 1,09 kWh/km uit de accu + 6% laadverlies</t>
         </is>
       </c>
     </row>

--- a/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
+++ b/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
@@ -81,14 +81,14 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -153,9 +153,9 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G92"/>
+  <dimension ref="B1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1473,11 +1473,11 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Bandbreedte € 0,07 - € 0,14; circa € 0,10 in 2026. Aantoonbaar hernieuwbaar levert de bovenkant op</t>
+          <t>NETSTROOM: € 0,07 - € 0,10 in 2026 (netmix telt voor circa 50% hernieuwbaar). Eigen zon rechtstreeks op de laadpaal verdubbelt dit ongeveer</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>8. UITKOMST MET ERE</t>
+          <t>8. UITKOMST MET ERE, ZONDER RESTWAARDE</t>
         </is>
       </c>
       <c r="C89" s="5" t="n"/>
@@ -1544,18 +1544,189 @@
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
+          <t>Terugverdientijd (jaren)</t>
+        </is>
+      </c>
+      <c r="C91" s="24">
+        <f>IF(C90&lt;=0,"nooit",C56/C90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>9. RESTWAARDE</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Economische levensduur (jaren)</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Panteia Input-Output Module D36</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Restwaarde e-truck (% van bruto aanschaf)</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Panteia leeftijdstabel, 7 jaar. ONZEKER — de tweedehandsmarkt voor e-trucks is nog dun</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Restwaarde dieseltruck (% van bruto aanschaf)</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Panteia leeftijdstabel, 7 jaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Restwaarde laadinfrastructuur (% van bruto)</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Lineair over de afschrijftermijn van 10 jaar die Panteia voor laadinfra hanteert</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Restwaarde e-trucks</t>
+        </is>
+      </c>
+      <c r="C98" s="21">
+        <f>$C$13*C95*$C$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Af: gederfde restwaarde dieseltrucks</t>
+        </is>
+      </c>
+      <c r="C99" s="21">
+        <f>-$C$14*C96*$C$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Restwaarde laadinfrastructuur</t>
+        </is>
+      </c>
+      <c r="C100" s="21">
+        <f>$C$26*C97</f>
+        <v/>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Over de bruto investering — de marktwaarde staat los van de ontvangen subsidie</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Totale extra restwaarde (in jaar 7)</t>
+        </is>
+      </c>
+      <c r="C101" s="22">
+        <f>C98+C99+C100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Omgeslagen per jaar</t>
+        </is>
+      </c>
+      <c r="C102" s="21">
+        <f>IF($C$94&lt;=0,0,C101/$C$94)</f>
+        <v/>
+      </c>
+      <c r="E102" s="26" t="inlineStr">
+        <is>
+          <t>Let op: dit bedrag komt pas vrij bij verkoop in jaar 7, niet elk jaar in kas</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>10. UITKOMST MET ERE EN RESTWAARDE</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Besparing per jaar inclusief restwaarde</t>
+        </is>
+      </c>
+      <c r="C105" s="21">
+        <f>C90+C102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="6" t="inlineStr">
+        <is>
           <t>TERUGVERDIENTIJD (jaren)</t>
         </is>
       </c>
-      <c r="C91" s="26">
-        <f>IF(C90&lt;=0,"nooit",C56/C90)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="27" t="inlineStr">
-        <is>
-          <t>Restwaarde staat aan beide kanten op nul. Accuvervanging, financieringskosten en ETS2 zitten er niet in.</t>
+      <c r="C106" s="27">
+        <f>IF(C105&lt;=0,"nooit",C56/C105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="26" t="inlineStr">
+        <is>
+          <t>Accuvervanging, financieringskosten en ETS2 zitten er niet in. Zie het document, par. 6.8.</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1997,7 @@
           <t>N3 Trekker</t>
         </is>
       </c>
-      <c r="K10" s="27" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>VERVANGEN — Volvo ERS 18-08-2026, route Ens-Naaldwijk: 1,09 kWh/km uit de accu + 6% laadverlies</t>
         </is>
@@ -2384,7 +2555,7 @@
         <v>60000</v>
       </c>
       <c r="C6" s="21">
-        <f>(B6*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B6*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <f>(B6*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B6*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
         <v/>
       </c>
       <c r="D6" s="39">
@@ -2397,7 +2568,7 @@
         <v>80000</v>
       </c>
       <c r="C7" s="21">
-        <f>(B7*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B7*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <f>(B7*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B7*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
         <v/>
       </c>
       <c r="D7" s="39">
@@ -2410,7 +2581,7 @@
         <v>100000</v>
       </c>
       <c r="C8" s="21">
-        <f>(B8*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B8*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <f>(B8*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B8*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
         <v/>
       </c>
       <c r="D8" s="39">
@@ -2423,7 +2594,7 @@
         <v>120000</v>
       </c>
       <c r="C9" s="21">
-        <f>(B9*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B9*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <f>(B9*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B9*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
         <v/>
       </c>
       <c r="D9" s="39">
@@ -2436,7 +2607,7 @@
         <v>150000</v>
       </c>
       <c r="C10" s="21">
-        <f>(B10*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B10*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <f>(B10*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B10*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
         <v/>
       </c>
       <c r="D10" s="39">
@@ -2449,7 +2620,7 @@
         <v>180000</v>
       </c>
       <c r="C11" s="21">
-        <f>(B11*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B11*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <f>(B11*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B11*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
         <v/>
       </c>
       <c r="D11" s="39">
@@ -2462,7 +2633,7 @@
         <v>200000</v>
       </c>
       <c r="C12" s="21">
-        <f>(B12*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B12*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)</f>
+        <f>(B12*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B12*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
         <v/>
       </c>
       <c r="D12" s="39">
@@ -2502,7 +2673,7 @@
         <v>0.11</v>
       </c>
       <c r="C17" s="21">
-        <f>Model!$C$90+(Model!$C$19-B17)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <f>Model!$C$105+(Model!$C$19-B17)*Model!$C$8*Model!$C$32*Model!$C$7</f>
         <v/>
       </c>
       <c r="D17" s="39">
@@ -2515,7 +2686,7 @@
         <v>0.14</v>
       </c>
       <c r="C18" s="21">
-        <f>Model!$C$90+(Model!$C$19-B18)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <f>Model!$C$105+(Model!$C$19-B18)*Model!$C$8*Model!$C$32*Model!$C$7</f>
         <v/>
       </c>
       <c r="D18" s="39">
@@ -2528,7 +2699,7 @@
         <v>0.16</v>
       </c>
       <c r="C19" s="21">
-        <f>Model!$C$90+(Model!$C$19-B19)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <f>Model!$C$105+(Model!$C$19-B19)*Model!$C$8*Model!$C$32*Model!$C$7</f>
         <v/>
       </c>
       <c r="D19" s="39">
@@ -2541,7 +2712,7 @@
         <v>0.18</v>
       </c>
       <c r="C20" s="21">
-        <f>Model!$C$90+(Model!$C$19-B20)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <f>Model!$C$105+(Model!$C$19-B20)*Model!$C$8*Model!$C$32*Model!$C$7</f>
         <v/>
       </c>
       <c r="D20" s="39">
@@ -2554,7 +2725,7 @@
         <v>0.2154</v>
       </c>
       <c r="C21" s="21">
-        <f>Model!$C$90+(Model!$C$19-B21)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <f>Model!$C$105+(Model!$C$19-B21)*Model!$C$8*Model!$C$32*Model!$C$7</f>
         <v/>
       </c>
       <c r="D21" s="39">
@@ -2567,7 +2738,7 @@
         <v>0.25</v>
       </c>
       <c r="C22" s="21">
-        <f>Model!$C$90+(Model!$C$19-B22)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <f>Model!$C$105+(Model!$C$19-B22)*Model!$C$8*Model!$C$32*Model!$C$7</f>
         <v/>
       </c>
       <c r="D22" s="39">
@@ -2580,7 +2751,7 @@
         <v>0.3</v>
       </c>
       <c r="C23" s="21">
-        <f>Model!$C$90+(Model!$C$19-B23)*Model!$C$8*Model!$C$32*Model!$C$7</f>
+        <f>Model!$C$105+(Model!$C$19-B23)*Model!$C$8*Model!$C$32*Model!$C$7</f>
         <v/>
       </c>
       <c r="D23" s="39">
@@ -2620,7 +2791,7 @@
         <v>2.9</v>
       </c>
       <c r="C28" s="21">
-        <f>Model!$C$90+(1/B28-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <f>Model!$C$105+(1/B28-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
         <v/>
       </c>
       <c r="D28" s="39">
@@ -2633,7 +2804,7 @@
         <v>3.2</v>
       </c>
       <c r="C29" s="21">
-        <f>Model!$C$90+(1/B29-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <f>Model!$C$105+(1/B29-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
         <v/>
       </c>
       <c r="D29" s="39">
@@ -2646,7 +2817,7 @@
         <v>3.5</v>
       </c>
       <c r="C30" s="21">
-        <f>Model!$C$90+(1/B30-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <f>Model!$C$105+(1/B30-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
         <v/>
       </c>
       <c r="D30" s="39">
@@ -2659,7 +2830,7 @@
         <v>3.8</v>
       </c>
       <c r="C31" s="21">
-        <f>Model!$C$90+(1/B31-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <f>Model!$C$105+(1/B31-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
         <v/>
       </c>
       <c r="D31" s="39">
@@ -2672,7 +2843,7 @@
         <v>4.1</v>
       </c>
       <c r="C32" s="21">
-        <f>Model!$C$90+(1/B32-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <f>Model!$C$105+(1/B32-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
         <v/>
       </c>
       <c r="D32" s="39">
@@ -2685,7 +2856,7 @@
         <v>4.5</v>
       </c>
       <c r="C33" s="21">
-        <f>Model!$C$90+(1/B33-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <f>Model!$C$105+(1/B33-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
         <v/>
       </c>
       <c r="D33" s="39">
@@ -2698,7 +2869,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="21">
-        <f>Model!$C$90+(1/B34-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
+        <f>Model!$C$105+(1/B34-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
         <v/>
       </c>
       <c r="D34" s="39">
@@ -2754,7 +2925,7 @@
         <v/>
       </c>
       <c r="E39" s="39">
-        <f>IF(Model!$C$90&lt;=0,"nooit",D39/Model!$C$90)</f>
+        <f>IF(Model!$C$105&lt;=0,"nooit",D39/Model!$C$105)</f>
         <v/>
       </c>
     </row>
@@ -2773,7 +2944,7 @@
         <v/>
       </c>
       <c r="E40" s="39">
-        <f>IF(Model!$C$90&lt;=0,"nooit",D40/Model!$C$90)</f>
+        <f>IF(Model!$C$105&lt;=0,"nooit",D40/Model!$C$105)</f>
         <v/>
       </c>
     </row>
@@ -2792,7 +2963,7 @@
         <v/>
       </c>
       <c r="E41" s="39">
-        <f>IF(Model!$C$90&lt;=0,"nooit",D41/Model!$C$90)</f>
+        <f>IF(Model!$C$105&lt;=0,"nooit",D41/Model!$C$105)</f>
         <v/>
       </c>
     </row>

--- a/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
+++ b/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
@@ -19,9 +19,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="€#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="€#,##0;(€#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="€#,##0;(€#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="€#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="€#,##0.00;(€#,##0.00);-"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
@@ -77,6 +77,11 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -84,11 +89,6 @@
       <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,38 +137,37 @@
     <xf numFmtId="3" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -534,27 +533,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G107"/>
+  <dimension ref="B1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="96" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="104" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>TCO elektrische vrachtwagens — gekalibreerd op TCO-ZET-Vracht v7.3 (Panteia / Topsector Logistiek)</t>
+          <t>TCO elektrische vrachtwagens — Kwekerij Baas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>A. Baas Potplantenkwekerij B.V. — 2 trucks · AanZET 2026 + SPRILA</t>
+          <t>Bronnen: Panteia TCO-ZET-Vracht v7.3 · Volvo Electric Range Simulator 18-08-2026 · Volvo calculatietool diesel/LNG/electric · opgaven Kwekerij Baas</t>
         </is>
       </c>
     </row>
@@ -566,14 +565,14 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Geel/blauw = zelf invullen · zwart = formule · groen = automatisch uit blad Panteia-parameters</t>
+          <t>Geel/blauw = invoer · zwart = formule · groen = uit het blad Panteia-parameters</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1. INVOER</t>
+          <t>1. ALGEMEEN</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -603,7 +602,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Opgave Kwekerij Baas</t>
+          <t>Opgave Kwekerij Baas. Werkelijke dagritten wijzen op 117.000 tot 142.000 — zie doc §6e</t>
         </is>
       </c>
     </row>
@@ -620,7 +619,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Klein / Middelgroot / Groot — geldt voor de HELE groep, geconsolideerd</t>
+          <t>60 medewerkers, € 22 mln omzet → middelgroot. Klein bij &lt; 50 arbeidsjaren</t>
         </is>
       </c>
     </row>
@@ -637,263 +636,226 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Kies uit blad Panteia-parameters. Stuurt verbruik, onderhoud, banden en AanZET-categorie aan</t>
+          <t>Stuurt verbruik, banden, MRB en AanZET-categorie aan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Dieselverbruik — 1 op ...</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>3.8</v>
+          <t>Economische levensduur (jaren)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Opgave Kwekerij Baas</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → liter per km</t>
-        </is>
-      </c>
-      <c r="C12" s="10">
-        <f>IF($C$11=0,0,1/$C$11)</f>
-        <v/>
+          <t>Volvo calculatietool: 60 maanden. Panteia hanteert 7 jaar</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Bruto aanschafprijs e-truck</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Opgave Nijwa: Volvo FH Aero Electric 4x2. De 6x2 kost € 320.000</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2. VOERTUIGPRIJZEN EN RESTWAARDE</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Bruto aanschafprijs vergelijkbare diesel</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>146166</v>
+          <t>Bruto aanschafprijs e-truck</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>300000</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Panteia casco 'Zware trekker z/opl'. OPVRAGEN bij Nijwa — bepaalt het staatssteunplafond</t>
+          <t>Opgave Nijwa: FH Aero Electric 4x2. De 6x2 kost € 320.000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Netto dieselprijs per liter</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>1.7</v>
+          <t>Bruto aanschafprijs vergelijkbare diesel</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>150000</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Opgave Kwekerij Baas</t>
+          <t>Volvo calculatietool</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Aandeel eigen opwek (zon + accu)</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>1</v>
+          <t>Restwaarde e-truck</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>20000</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Opgave Kwekerij Baas — volledig eigen opwek</t>
+          <t>Volvo calculatietool — 6,7% van de nieuwprijs na 5 jaar / 500.000 km</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Prijs eigen opwek per kWh</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>0.1</v>
+          <t>Restwaarde dieseltruck</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>25000</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Opgave Kwekerij Baas</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Prijs netstroom per kWh</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>0.21537</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Panteia Parameters D6</t>
+          <t>Volvo calculatietool — 16,7% na 5 jaar</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → gemengde stroomprijs</t>
-        </is>
-      </c>
-      <c r="C19" s="14">
-        <f>$C$16*$C$17+(1-$C$16)*$C$18</f>
-        <v/>
-      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>3. ENERGIE</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Vrachtwagenheffing diesel (€/km)</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>0.19</v>
+          <t>Dieselverbruik — 1 op ...</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>3.8</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Per 1 juli 2026 — zit NIET in de Panteia-tool v7.3</t>
+          <t>Opgave Kwekerij Baas. Volvo rekent met 25 l/100 km = 1 op 4,0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Vrachtwagenheffing zero-emissie (€/km)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Per 1 juli 2026 — circa 80% korting</t>
-        </is>
+          <t xml:space="preserve">  → liter per km</t>
+        </is>
+      </c>
+      <c r="C21" s="11">
+        <f>IF($C$20=0,0,1/$C$20)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Extra chauffeurskosten elektrisch per jaar</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>3655</v>
+          <t>Netto dieselprijs per liter</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>1.7</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Wachttijd bij laden. Panteia rekent +4,1% (E118 vs D118). Schaalt mee met de inzet</t>
+          <t>Opgave Kwekerij Baas. Volvo rekent met € 1,77</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Vennootschapsbelasting</t>
+          <t>Aandeel eigen opwek</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>0.258</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tarief 2026</t>
+          <t>Opgave Kwekerij Baas — ORC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>EIA-aftrekpercentage</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>0.4</v>
+          <t>Prijs eigen opwek per kWh</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>0.1</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>EIA 2026</t>
+          <t>Opgave Kwekerij Baas</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>EIA-grondslag = volledige aanschafprijs?</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Nee</t>
-        </is>
+          <t>Prijs netstroom per kWh</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>0.2154</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Nee = alleen de meerprijs (voorzichtig). Ja = hele aanschafprijs, zoals Panteia bij MIA doet</t>
+          <t>Panteia. Volvo rekent met € 0,30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Investering laadinfrastructuur</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>461500</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Offerte Draccu DR283: accu 1.045 kWh + 3x DC 240 kW</t>
-        </is>
+          <t xml:space="preserve">  → gemengde stroomprijs</t>
+        </is>
+      </c>
+      <c r="C26" s="14">
+        <f>$C$23*$C$24+(1-$C$23)*$C$25</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>SPRILA-subsidie</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>178000</v>
+          <t>AdBlue per jaar (diesel)</t>
+        </is>
+      </c>
+      <c r="C27" s="15">
+        <f>$C$8/100*2.5*0.73</f>
+        <v/>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Volgens de RVO-bedragen 2026. LET OP: de Panteia-tool hanteert afwijkende SPRILA-bedragen</t>
+          <t>Volvo: 2,5 l per 100 km à € 0,73</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2. UIT HET VOERTUIGTYPE (Panteia)</t>
+          <t>4. HEFFINGEN, ONDERHOUD EN OVERIG</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -905,828 +867,980 @@
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>AanZET-categorie</t>
-        </is>
-      </c>
-      <c r="C30" s="15">
-        <f>INDEX('Panteia-parameters'!$J$6:$J$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
-        <v/>
+          <t>Tolkilometers Nederland per jaar</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Volvo calculatietool — niet elke kilometer is tolplichtig</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Panteia-verbruik diesel (l/km) — referentie</t>
-        </is>
-      </c>
-      <c r="C31" s="16">
-        <f>INDEX('Panteia-parameters'!$C$6:$C$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
-        <v/>
+          <t>Vrachtwagenheffing diesel (€/km)</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>0.201</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Ter vergelijking met jullie eigen 1 op-cijfer hierboven</t>
+          <t>Volvo 2026-tarief, CO2-klasse 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Stroomverbruik e-truck (kWh/km)</t>
-        </is>
-      </c>
-      <c r="C32" s="17">
-        <f>INDEX('Panteia-parameters'!$D$6:$D$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
-        <v/>
+          <t>Vrachtwagenheffing zero-emissie (€/km)</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>0.038</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Inclusief laadverliezen</t>
+          <t>Volvo 2026-tarief, CO2-klasse 5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Onderhoud diesel (€/km)</t>
-        </is>
-      </c>
-      <c r="C33" s="18">
-        <f>INDEX('Panteia-parameters'!$E$6:$E$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
-        <v/>
+          <t>Tolkilometers Duitsland per jaar</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Volvo calculatietool. Bij ritten uitsluitend in NL is dit 0</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Onderhoud elektrisch (€/km)</t>
-        </is>
-      </c>
-      <c r="C34" s="18">
-        <f>INDEX('Panteia-parameters'!$F$6:$F$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
-        <v/>
+          <t>MAUT diesel (€/km)</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Volvo 2026-tarief</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Reparaties per jaar (beide)</t>
-        </is>
-      </c>
-      <c r="C35" s="19">
-        <f>INDEX('Panteia-parameters'!$G$6:$G$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
-        <v/>
+          <t>MAUT zero-emissie (€/km)</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Zero-emissie is vrijgesteld</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Banden (€/km, beide)</t>
-        </is>
-      </c>
-      <c r="C36" s="18">
-        <f>INDEX('Panteia-parameters'!$H$6:$H$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
-        <v/>
+          <t>Onderhoud + reparatie diesel per jaar</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Volvo: € 600 per maand. Panteia komt op € 10.818</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Motorrijtuigenbelasting per jaar</t>
-        </is>
-      </c>
-      <c r="C37" s="19">
-        <f>INDEX('Panteia-parameters'!$I$6:$I$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
-        <v/>
+          <t>Onderhoud + reparatie elektrisch per jaar</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>7740</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Gelijk verondersteld voor diesel en elektrisch — valt vanaf 1-7-2026 terug naar het EU-minimum</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>3. AANZET-SUBSIDIE</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
+          <t>Volvo: € 645 per maand — DUURDER dan diesel. Panteia komt juist op € 6.236. Zie doc §6.7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Extra chauffeurskosten elektrisch per jaar</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>3655</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Wachttijd bij laden; Panteia rekent +4,1%</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Subsidiepercentage</t>
-        </is>
-      </c>
-      <c r="C40" s="20">
-        <f>SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,$C$30,'Panteia-parameters'!$D$16:$D$27,$C$9)</f>
-        <v/>
-      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>5. SUBSIDIE, FISCAAL EN LAADINFRASTRUCTUUR</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Maximum per voertuig</t>
-        </is>
-      </c>
-      <c r="C41" s="21">
-        <f>SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,$C$30,'Panteia-parameters'!$D$16:$D$27,$C$9)</f>
-        <v/>
+          <t>Vennootschapsbelasting</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Tarief 2026</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Meerprijs t.o.v. diesel</t>
-        </is>
-      </c>
-      <c r="C42" s="21">
-        <f>MAX(0,$C$13-$C$14)</f>
-        <v/>
+          <t>EIA-aftrekpercentage</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>EIA 2026</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Staatssteunplafond (% van meerprijs)</t>
-        </is>
-      </c>
-      <c r="C43" s="20">
-        <f>INDEX('Panteia-parameters'!$D$31:$D$33,MATCH($C$9,'Panteia-parameters'!$C$31:$C$33,0))</f>
-        <v/>
+          <t>EIA-grondslag = volledige aanschafprijs?</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Nee = alleen de meerprijs (voorzichtig)</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Staatssteunplafond in euro</t>
-        </is>
-      </c>
-      <c r="C44" s="21">
-        <f>C43*C42</f>
-        <v/>
+          <t>Investering laadinfrastructuur (bruto)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>461500</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Offerte Draccu DR283</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>AanZET per truck</t>
-        </is>
-      </c>
-      <c r="C45" s="22">
-        <f>MIN($C$13*C40,C41,C44)</f>
-        <v/>
+          <t>SPRILA-subsidie</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>178000</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Drie plafonds tegelijk — dezelfde MIN-constructie als M2-Subsidie!B20</t>
+          <t>TOEGEKEND 21-08-2026, beschikking SPRILA26-04007812</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>AanZET totaal</t>
-        </is>
-      </c>
-      <c r="C46" s="22">
-        <f>C45*$C$7</f>
-        <v/>
+          <t>Restwaarde laadinfrastructuur</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>92300</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>20% van bruto. Alleen de hardware heeft restwaarde; het aanlegwerk niet</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Welk plafond bijt?</t>
-        </is>
-      </c>
-      <c r="C47" s="23">
-        <f>IF(C45=C44,"staatssteunplafond",IF(C45=C41,"maximum per voertuig","percentage"))</f>
-        <v/>
+          <t>ERE-waarde per geladen kWh</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Netstroom: € 0,07–0,10 (netmix telt voor ca. 50% hernieuwbaar). Aantoonbaar eigen zon verdubbelt dit</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Commissie inboekdienstverlener</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>AANNAME — offertes opvragen</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>4. EXTRA INVESTERING TEN OPZICHTE VAN DIESEL</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Meerprijs per truck</t>
-        </is>
-      </c>
-      <c r="C50" s="21">
-        <f>C42</f>
-        <v/>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Disconteringsvoet voor contante waarde</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Volvo rekent met 6% rente</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>EIA-grondslag per truck</t>
-        </is>
-      </c>
-      <c r="C51" s="21">
-        <f>MAX(0,IF($C$25="Ja",$C$13,C50)-C45)</f>
-        <v/>
-      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>6. UIT HET VOERTUIGTYPE (Panteia)</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>EIA-voordeel per truck (kaseffect)</t>
-        </is>
-      </c>
-      <c r="C52" s="21">
-        <f>C51*$C$24*$C$23</f>
+          <t>AanZET-categorie</t>
+        </is>
+      </c>
+      <c r="C52" s="16">
+        <f>INDEX('Panteia-parameters'!$H$6:$H$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Netto meerprijs per truck</t>
-        </is>
-      </c>
-      <c r="C53" s="21">
-        <f>C50-C45-C52</f>
-        <v/>
+          <t>Stroomverbruik e-truck (kWh/km)</t>
+        </is>
+      </c>
+      <c r="C53" s="17">
+        <f>INDEX('Panteia-parameters'!$C$6:$C$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
+        <v/>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Volvo ERS, incl. laadverlies</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Netto meerprijs alle trucks</t>
-        </is>
-      </c>
-      <c r="C54" s="21">
-        <f>C53*$C$7</f>
+          <t>Banden (€/km, beide)</t>
+        </is>
+      </c>
+      <c r="C54" s="18">
+        <f>INDEX('Panteia-parameters'!$D$6:$D$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Laadinfrastructuur na SPRILA</t>
-        </is>
-      </c>
-      <c r="C55" s="21">
-        <f>$C$26-$C$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>TOTALE EXTRA INVESTERING</t>
-        </is>
-      </c>
-      <c r="C56" s="22">
-        <f>C54+C55</f>
-        <v/>
-      </c>
+          <t>Motorrijtuigenbelasting per jaar (beide)</t>
+        </is>
+      </c>
+      <c r="C55" s="19">
+        <f>INDEX('Panteia-parameters'!$E$6:$E$10,MATCH($C$10,'Panteia-parameters'!$B$6:$B$10,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>7. AANZET-SUBSIDIE</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>5. JAARLIJKSE EXPLOITATIEKOSTEN PER TRUCK</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n"/>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Subsidiepercentage</t>
+        </is>
+      </c>
+      <c r="C58" s="20">
+        <f>SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,$C$52,'Panteia-parameters'!$D$16:$D$27,$C$9)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Diesel — brandstof</t>
-        </is>
-      </c>
-      <c r="C59" s="21">
-        <f>$C$8*$C$12*$C$15</f>
+          <t>Maximum per voertuig</t>
+        </is>
+      </c>
+      <c r="C59" s="15">
+        <f>SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,$C$52,'Panteia-parameters'!$D$16:$D$27,$C$9)</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Diesel — vrachtwagenheffing</t>
-        </is>
-      </c>
-      <c r="C60" s="21">
-        <f>$C$8*$C$20</f>
+          <t>Meerprijs t.o.v. diesel</t>
+        </is>
+      </c>
+      <c r="C60" s="15">
+        <f>MAX(0,$C$14-$C$15)</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Diesel — onderhoud</t>
-        </is>
-      </c>
-      <c r="C61" s="21">
-        <f>$C$8*C33</f>
+          <t>Staatssteunplafond (% van meerprijs)</t>
+        </is>
+      </c>
+      <c r="C61" s="20">
+        <f>INDEX('Panteia-parameters'!$D$31:$D$33,MATCH($C$9,'Panteia-parameters'!$C$31:$C$33,0))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Diesel — banden</t>
-        </is>
-      </c>
-      <c r="C62" s="21">
-        <f>$C$8*C36</f>
+          <t>Staatssteunplafond in euro</t>
+        </is>
+      </c>
+      <c r="C62" s="15">
+        <f>C61*C60</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Diesel — reparaties</t>
+          <t>AanZET per truck</t>
         </is>
       </c>
       <c r="C63" s="21">
-        <f>C35</f>
+        <f>MIN($C$14*C58,C59,C62)</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Diesel — motorrijtuigenbelasting</t>
+          <t>AanZET totaal</t>
         </is>
       </c>
       <c r="C64" s="21">
-        <f>C37</f>
+        <f>C63*$C$7</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Diesel totaal</t>
+          <t>Welk plafond bijt?</t>
         </is>
       </c>
       <c r="C65" s="22">
-        <f>SUM(C59:C64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Elektrisch — stroom</t>
-        </is>
-      </c>
-      <c r="C66" s="21">
-        <f>$C$8*C32*$C$19</f>
+        <f>IF(C63=C62,"staatssteunplafond",IF(C63=C59,"maximum per voertuig","percentage"))</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Elektrisch — vrachtwagenheffing</t>
-        </is>
-      </c>
-      <c r="C67" s="21">
-        <f>$C$8*$C$21</f>
-        <v/>
-      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>8. EXTRA INVESTERING</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch — onderhoud</t>
-        </is>
-      </c>
-      <c r="C68" s="21">
-        <f>$C$8*C34</f>
+          <t>Meerprijs per truck</t>
+        </is>
+      </c>
+      <c r="C68" s="15">
+        <f>C60</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch — banden</t>
-        </is>
-      </c>
-      <c r="C69" s="21">
-        <f>$C$8*C36</f>
+          <t>EIA-grondslag per truck</t>
+        </is>
+      </c>
+      <c r="C69" s="15">
+        <f>MAX(0,IF($C$43="Ja",$C$14,C68)-C63)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch — reparaties</t>
-        </is>
-      </c>
-      <c r="C70" s="21">
-        <f>C35</f>
+          <t>EIA-voordeel per truck</t>
+        </is>
+      </c>
+      <c r="C70" s="15">
+        <f>C69*$C$42*$C$41</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch — motorrijtuigenbelasting</t>
-        </is>
-      </c>
-      <c r="C71" s="21">
-        <f>C37</f>
+          <t>Netto meerprijs per truck</t>
+        </is>
+      </c>
+      <c r="C71" s="15">
+        <f>C68-C63-C70</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch — extra chauffeurskosten</t>
-        </is>
-      </c>
-      <c r="C72" s="21">
-        <f>$C$22</f>
+          <t>Netto meerprijs alle trucks</t>
+        </is>
+      </c>
+      <c r="C72" s="15">
+        <f>C71*$C$7</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Elektrisch totaal</t>
-        </is>
-      </c>
-      <c r="C73" s="22">
-        <f>SUM(C66:C72)</f>
+          <t>Laadinfrastructuur na SPRILA</t>
+        </is>
+      </c>
+      <c r="C73" s="15">
+        <f>$C$44-$C$45</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Besparing per truck per jaar</t>
+          <t>TOTALE EXTRA INVESTERING</t>
         </is>
       </c>
       <c r="C74" s="21">
-        <f>C65-C73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Besparing alle trucks per jaar</t>
-        </is>
-      </c>
-      <c r="C75" s="22">
-        <f>C74*$C$7</f>
-        <v/>
-      </c>
+        <f>C72+C73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>9. JAARLIJKSE EXPLOITATIEKOSTEN PER TRUCK</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>6. UITKOMST ZONDER ERE</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Diesel — brandstof</t>
+        </is>
+      </c>
+      <c r="C77" s="15">
+        <f>$C$8*$C$21*$C$22</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Totale extra investering</t>
-        </is>
-      </c>
-      <c r="C78" s="21">
-        <f>C56</f>
+          <t>Diesel — AdBlue</t>
+        </is>
+      </c>
+      <c r="C78" s="15">
+        <f>$C$27</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Besparing per jaar</t>
-        </is>
-      </c>
-      <c r="C79" s="21">
-        <f>C75</f>
+          <t>Diesel — vrachtwagenheffing NL</t>
+        </is>
+      </c>
+      <c r="C79" s="15">
+        <f>$C$30*$C$31</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Terugverdientijd (jaren)</t>
-        </is>
-      </c>
-      <c r="C80" s="24">
-        <f>IF(C79&lt;=0,"nooit",C56/C79)</f>
+          <t>Diesel — MAUT Duitsland</t>
+        </is>
+      </c>
+      <c r="C80" s="15">
+        <f>$C$33*$C$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Diesel — onderhoud en reparatie</t>
+        </is>
+      </c>
+      <c r="C81" s="15">
+        <f>$C$36</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>7. ERE — EMISSIEREDUCTIE-EENHEDEN</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="n"/>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Diesel — banden</t>
+        </is>
+      </c>
+      <c r="C82" s="15">
+        <f>$C$8*C54</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Geladen kWh per jaar (beide trucks)</t>
-        </is>
-      </c>
-      <c r="C83" s="25">
-        <f>$C$8*C32*$C$7</f>
+          <t>Diesel — motorrijtuigenbelasting</t>
+        </is>
+      </c>
+      <c r="C83" s="15">
+        <f>C55</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>ERE-waarde per geladen kWh</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>NETSTROOM: € 0,07 - € 0,10 in 2026 (netmix telt voor circa 50% hernieuwbaar). Eigen zon rechtstreeks op de laadpaal verdubbelt dit ongeveer</t>
-        </is>
+          <t>Diesel totaal</t>
+        </is>
+      </c>
+      <c r="C84" s="21">
+        <f>SUM(C77:C83)</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Commissie inboekdienstverlener</t>
-        </is>
-      </c>
-      <c r="C85" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>AANNAME — opvragen. Inboeken kan alleen via een dienstverlener, tenzij je zelf &gt; 2 mln kWh per jaar laadt</t>
-        </is>
+          <t>Elektrisch — stroom</t>
+        </is>
+      </c>
+      <c r="C85" s="15">
+        <f>$C$8*C53*$C$26</f>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Bruto ERE-opbrengst per jaar</t>
-        </is>
-      </c>
-      <c r="C86" s="21">
-        <f>C83*C84</f>
+          <t>Elektrisch — vrachtwagenheffing NL</t>
+        </is>
+      </c>
+      <c r="C86" s="15">
+        <f>$C$30*$C$32</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Netto ERE-opbrengst per jaar</t>
-        </is>
-      </c>
-      <c r="C87" s="22">
-        <f>C86*(1-C85)</f>
+          <t>Elektrisch — MAUT Duitsland</t>
+        </is>
+      </c>
+      <c r="C87" s="15">
+        <f>$C$33*$C$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — onderhoud en reparatie</t>
+        </is>
+      </c>
+      <c r="C88" s="15">
+        <f>$C$37</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>8. UITKOMST MET ERE, ZONDER RESTWAARDE</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="5" t="n"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch — banden</t>
+        </is>
+      </c>
+      <c r="C89" s="15">
+        <f>$C$8*C54</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Besparing per jaar inclusief ERE</t>
-        </is>
-      </c>
-      <c r="C90" s="21">
-        <f>C75+C87</f>
+          <t>Elektrisch — motorrijtuigenbelasting</t>
+        </is>
+      </c>
+      <c r="C90" s="15">
+        <f>C55</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Terugverdientijd (jaren)</t>
-        </is>
-      </c>
-      <c r="C91" s="24">
-        <f>IF(C90&lt;=0,"nooit",C56/C90)</f>
+          <t>Elektrisch — extra chauffeurskosten</t>
+        </is>
+      </c>
+      <c r="C91" s="15">
+        <f>$C$38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Elektrisch totaal</t>
+        </is>
+      </c>
+      <c r="C92" s="21">
+        <f>SUM(C85:C91)</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>9. RESTWAARDE</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Besparing per truck per jaar</t>
+        </is>
+      </c>
+      <c r="C93" s="15">
+        <f>C84-C92</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Economische levensduur (jaren)</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Panteia Input-Output Module D36</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Restwaarde e-truck (% van bruto aanschaf)</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Panteia leeftijdstabel, 7 jaar. ONZEKER — de tweedehandsmarkt voor e-trucks is nog dun</t>
-        </is>
+          <t>Besparing alle trucks per jaar</t>
+        </is>
+      </c>
+      <c r="C94" s="21">
+        <f>C93*$C$7</f>
+        <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>Restwaarde dieseltruck (% van bruto aanschaf)</t>
-        </is>
-      </c>
-      <c r="C96" s="13" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>Panteia leeftijdstabel, 7 jaar</t>
-        </is>
-      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>10. ERE</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Restwaarde laadinfrastructuur (% van bruto)</t>
-        </is>
-      </c>
-      <c r="C97" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Lineair over de afschrijftermijn van 10 jaar die Panteia voor laadinfra hanteert</t>
-        </is>
+          <t>Geladen kWh per jaar (beide trucks)</t>
+        </is>
+      </c>
+      <c r="C97" s="23">
+        <f>$C$8*C53*$C$7</f>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Restwaarde e-trucks</t>
-        </is>
-      </c>
-      <c r="C98" s="21">
-        <f>$C$13*C95*$C$7</f>
+          <t>Bruto ERE-opbrengst per jaar</t>
+        </is>
+      </c>
+      <c r="C98" s="15">
+        <f>C97*$C$47</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Af: gederfde restwaarde dieseltrucks</t>
+          <t>Netto ERE-opbrengst per jaar</t>
         </is>
       </c>
       <c r="C99" s="21">
-        <f>-$C$14*C96*$C$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Restwaarde laadinfrastructuur</t>
-        </is>
-      </c>
-      <c r="C100" s="21">
-        <f>$C$26*C97</f>
-        <v/>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Over de bruto investering — de marktwaarde staat los van de ontvangen subsidie</t>
-        </is>
+        <f>C98*(1-$C$48)</f>
+        <v/>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Totale extra restwaarde (in jaar 7)</t>
-        </is>
-      </c>
-      <c r="C101" s="22">
-        <f>C98+C99+C100</f>
-        <v/>
-      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>11. RESTWAARDE</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Omgeslagen per jaar</t>
-        </is>
-      </c>
-      <c r="C102" s="21">
-        <f>IF($C$94&lt;=0,0,C101/$C$94)</f>
-        <v/>
-      </c>
-      <c r="E102" s="26" t="inlineStr">
-        <is>
-          <t>Let op: dit bedrag komt pas vrij bij verkoop in jaar 7, niet elk jaar in kas</t>
-        </is>
+          <t>Restwaarde e-trucks</t>
+        </is>
+      </c>
+      <c r="C102" s="15">
+        <f>$C$16*$C$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Af: gederfde restwaarde dieseltrucks</t>
+        </is>
+      </c>
+      <c r="C103" s="15">
+        <f>-$C$17*$C$7</f>
+        <v/>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>10. UITKOMST MET ERE EN RESTWAARDE</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="5" t="n"/>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Restwaarde laadinfrastructuur</t>
+        </is>
+      </c>
+      <c r="C104" s="15">
+        <f>$C$46</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Besparing per jaar inclusief restwaarde</t>
+          <t>Totale extra restwaarde (aan het einde)</t>
         </is>
       </c>
       <c r="C105" s="21">
-        <f>C90+C102</f>
+        <f>SUM(C102:C104)</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>TERUGVERDIENTIJD (jaren)</t>
-        </is>
-      </c>
-      <c r="C106" s="27">
-        <f>IF(C105&lt;=0,"nooit",C56/C105)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="26" t="inlineStr">
-        <is>
-          <t>Accuvervanging, financieringskosten en ETS2 zitten er niet in. Zie het document, par. 6.8.</t>
+          <t>Omgeslagen per jaar</t>
+        </is>
+      </c>
+      <c r="C106" s="15">
+        <f>IF($C$11&lt;=0,0,C105/$C$11)</f>
+        <v/>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Komt pas vrij bij verkoop, niet elk jaar in kas</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>12. UITKOMST</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Totale extra investering</t>
+        </is>
+      </c>
+      <c r="C109" s="15">
+        <f>C74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Besparing per jaar (exploitatie + ERE)</t>
+        </is>
+      </c>
+      <c r="C110" s="15">
+        <f>C94+C99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Terugverdientijd zonder restwaarde</t>
+        </is>
+      </c>
+      <c r="C111" s="24">
+        <f>IF(C110&lt;=0,"nooit",C74/C110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Besparing per jaar inclusief restwaarde</t>
+        </is>
+      </c>
+      <c r="C112" s="15">
+        <f>C110+C106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>TERUGVERDIENTIJD MET RESTWAARDE</t>
+        </is>
+      </c>
+      <c r="C113" s="25">
+        <f>IF(C112&lt;=0,"nooit",C74/C112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>13. CONTANTE WAARDE OVER DE LEVENSDUUR</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="5" t="n"/>
+      <c r="G115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>Contante waarde van de jaarbesparingen</t>
+        </is>
+      </c>
+      <c r="C116" s="15">
+        <f>IF($C$49=0,C110*$C$11,C110*(1-(1+$C$49)^-$C$11)/$C$49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Contante waarde van de restwaarde</t>
+        </is>
+      </c>
+      <c r="C117" s="15">
+        <f>C105/(1+$C$49)^$C$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>NETTO CONTANTE WAARDE</t>
+        </is>
+      </c>
+      <c r="C118" s="26">
+        <f>C116+C117-C74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>Hier zit de kapitaalkost wél in, via de disconteringsvoet. In de terugverdientijd hierboven niet.</t>
         </is>
       </c>
     </row>
@@ -1741,33 +1855,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K48"/>
+  <dimension ref="B1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="90" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="96" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="28" t="inlineStr">
         <is>
-          <t>Parameters overgenomen uit TCO-ZET-Vracht v7.3 (Panteia / Topsector Logistiek, 23-09-2024)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Basisjaar 2024. Blauw = letterlijk uit de tool, met broncel erbij.</t>
+          <t>Parameters uit TCO-ZET-Vracht v7.3 (Panteia / Topsector Logistiek, 23-09-2024)</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1890,6 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="29" t="inlineStr">
@@ -1794,40 +1899,20 @@
       </c>
       <c r="C5" s="29" t="inlineStr">
         <is>
-          <t>Diesel [l/km]</t>
+          <t>Elektrisch [kWh/km]</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>Elektrisch [kWh/km]</t>
+          <t>Banden [€/km]</t>
         </is>
       </c>
       <c r="E5" s="29" t="inlineStr">
         <is>
-          <t>Onderhoud diesel [€/km]</t>
-        </is>
-      </c>
-      <c r="F5" s="29" t="inlineStr">
-        <is>
-          <t>Onderhoud elektrisch [€/km]</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="inlineStr">
-        <is>
-          <t>Reparaties [€/jaar]</t>
+          <t>Wegenbelasting [€/jaar]</t>
         </is>
       </c>
       <c r="H5" s="29" t="inlineStr">
-        <is>
-          <t>Banden [€/km]</t>
-        </is>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
-        <is>
-          <t>Wegenbelasting [€/jaar]</t>
-        </is>
-      </c>
-      <c r="J5" s="29" t="inlineStr">
         <is>
           <t>AanZET-categorie</t>
         </is>
@@ -1840,27 +1925,15 @@
         </is>
       </c>
       <c r="C6" s="31" t="n">
-        <v>0.1323997619652777</v>
+        <v>0.4761551824999992</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>0.4761551824999992</v>
+        <v>0.023121345</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>0.05729283728200001</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>0.02864641864100001</v>
-      </c>
-      <c r="G6" s="34" t="n">
-        <v>551.25</v>
-      </c>
-      <c r="H6" s="33" t="n">
-        <v>0.023121345</v>
-      </c>
-      <c r="I6" s="34" t="n">
         <v>380</v>
       </c>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="H6" s="30" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
@@ -1873,27 +1946,15 @@
         </is>
       </c>
       <c r="C7" s="31" t="n">
-        <v>0.2106393949902324</v>
+        <v>0.9519194221532747</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>0.9519194221532747</v>
+        <v>0.0227691285</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>0.06302015160140001</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>0.0315100758007</v>
-      </c>
-      <c r="G7" s="34" t="n">
-        <v>551.25</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>0.0227691285</v>
-      </c>
-      <c r="I7" s="34" t="n">
         <v>380</v>
       </c>
-      <c r="J7" s="30" t="inlineStr">
+      <c r="H7" s="30" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &lt;= 18t)</t>
         </is>
@@ -1906,27 +1967,15 @@
         </is>
       </c>
       <c r="C8" s="31" t="n">
-        <v>0.2697424784835717</v>
+        <v>1.327285842517089</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>1.327285842517089</v>
+        <v>0.022416912</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>0.06874746592080001</v>
-      </c>
-      <c r="F8" s="33" t="n">
-        <v>0.03437373296040001</v>
-      </c>
-      <c r="G8" s="34" t="n">
-        <v>1102.5</v>
-      </c>
-      <c r="H8" s="33" t="n">
-        <v>0.022416912</v>
-      </c>
-      <c r="I8" s="34" t="n">
         <v>380</v>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &gt; 18t)</t>
         </is>
@@ -1939,27 +1988,15 @@
         </is>
       </c>
       <c r="C9" s="31" t="n">
-        <v>0.2794114755568611</v>
+        <v>1.299629854013712</v>
       </c>
       <c r="D9" s="32" t="n">
-        <v>1.299629854013712</v>
+        <v>0.03444994</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0.0801939981012</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>0.0400969990506</v>
-      </c>
-      <c r="G9" s="34" t="n">
-        <v>1653.75</v>
-      </c>
-      <c r="H9" s="33" t="n">
-        <v>0.03444994</v>
-      </c>
-      <c r="I9" s="34" t="n">
         <v>1028</v>
       </c>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="H9" s="30" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
@@ -1972,41 +2009,22 @@
         </is>
       </c>
       <c r="C10" s="31" t="n">
-        <v>0.3413502921361025</v>
+        <v>1.155</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>1.155</v>
+        <v>0.04648296799999999</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>0.09164053028160001</v>
-      </c>
-      <c r="F10" s="33" t="n">
-        <v>0.0458202651408</v>
-      </c>
-      <c r="G10" s="34" t="n">
-        <v>1653.75</v>
-      </c>
-      <c r="H10" s="33" t="n">
-        <v>0.04648296799999999</v>
-      </c>
-      <c r="I10" s="34" t="n">
         <v>1028</v>
       </c>
-      <c r="J10" s="30" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
-        <is>
-          <t>VERVANGEN — Volvo ERS 18-08-2026, route Ens-Naaldwijk: 1,09 kWh/km uit de accu + 6% laadverlies</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Bron: blad 'Invoer en categorieën', tabellen B21:K25 en B31:O35; categorie uit 'M2-Subsidie' F27:G31</t>
+      <c r="J10" s="27" t="inlineStr">
+        <is>
+          <t>VERVANGEN — Volvo ERS 18-08-2026, route Ens–Naaldwijk: 1,09 kWh/km uit de accu + 6% laadverlies</t>
         </is>
       </c>
     </row>
@@ -2022,254 +2040,254 @@
       <c r="F14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>AanZET-categorie</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>Ondernemingsgrootte</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>Max. steun [%]</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="34" t="inlineStr">
         <is>
           <t>Max. steun [€]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E16" s="37" t="n">
+      <c r="E16" s="36" t="n">
         <v>0.12</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="33" t="n">
         <v>14700</v>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="36" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="D17" s="36" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="E17" s="37" t="n">
+      <c r="E17" s="36" t="n">
         <v>0.148</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="33" t="n">
         <v>18800</v>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="E18" s="37" t="n">
+      <c r="E18" s="36" t="n">
         <v>0.061</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="33" t="n">
         <v>7500</v>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &lt;= 18t)</t>
         </is>
       </c>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="36" t="n">
         <v>0.2</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="33" t="n">
         <v>60500</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="36" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &lt;= 18t)</t>
         </is>
       </c>
-      <c r="D20" s="36" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="E20" s="37" t="n">
+      <c r="E20" s="36" t="n">
         <v>0.286</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="33" t="n">
         <v>86600</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &lt;= 18t)</t>
         </is>
       </c>
-      <c r="D21" s="36" t="inlineStr">
+      <c r="D21" s="35" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="E21" s="37" t="n">
+      <c r="E21" s="36" t="n">
         <v>0.103</v>
       </c>
-      <c r="F21" s="34" t="n">
+      <c r="F21" s="33" t="n">
         <v>31100</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="36" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &gt; 18t)</t>
         </is>
       </c>
-      <c r="D22" s="36" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E22" s="37" t="n">
+      <c r="E22" s="36" t="n">
         <v>0.21</v>
       </c>
-      <c r="F22" s="34" t="n">
+      <c r="F22" s="33" t="n">
         <v>83200</v>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="36" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &gt; 18t)</t>
         </is>
       </c>
-      <c r="D23" s="36" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="E23" s="37" t="n">
+      <c r="E23" s="36" t="n">
         <v>0.29</v>
       </c>
-      <c r="F23" s="34" t="n">
+      <c r="F23" s="33" t="n">
         <v>115200</v>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>N3 Bakwagen (lvm &gt; 18t)</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="E24" s="37" t="n">
+      <c r="E24" s="36" t="n">
         <v>0.111</v>
       </c>
-      <c r="F24" s="34" t="n">
+      <c r="F24" s="33" t="n">
         <v>43900</v>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
       </c>
-      <c r="D25" s="36" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
       </c>
-      <c r="E25" s="37" t="n">
+      <c r="E25" s="36" t="n">
         <v>0.21</v>
       </c>
-      <c r="F25" s="34" t="n">
+      <c r="F25" s="33" t="n">
         <v>83200</v>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="36" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
       </c>
-      <c r="D26" s="36" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
-      <c r="E26" s="37" t="n">
+      <c r="E26" s="36" t="n">
         <v>0.29</v>
       </c>
-      <c r="F26" s="34" t="n">
+      <c r="F26" s="33" t="n">
         <v>115200</v>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="36" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>N3 Trekker</t>
         </is>
       </c>
-      <c r="D27" s="36" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
       </c>
-      <c r="E27" s="37" t="n">
+      <c r="E27" s="36" t="n">
         <v>0.111</v>
       </c>
-      <c r="F27" s="34" t="n">
+      <c r="F27" s="33" t="n">
         <v>43900</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Bron: blad 'M2-Subsidie' F5:I17. Komt exact overeen met de bedragen die RVO en de dealers publiceren.</t>
+          <t>Bron: blad 'M2-Subsidie' F5:I17. Bevestigd door de beschikking van RVO.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>STAATSSTEUNPLAFOND — MAXIMALE STEUN ALS % VAN DE MEERPRIJS</t>
+          <t>STAATSSTEUNPLAFOND — % VAN DE MEERPRIJS</t>
         </is>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -2277,7 +2295,7 @@
       <c r="E30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="C31" s="36" t="inlineStr">
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>Groot</t>
         </is>
@@ -2287,7 +2305,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="36" t="inlineStr">
+      <c r="C32" s="35" t="inlineStr">
         <is>
           <t>Middelgroot</t>
         </is>
@@ -2297,195 +2315,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="36" t="inlineStr">
+      <c r="C33" s="35" t="inlineStr">
         <is>
           <t>Klein</t>
         </is>
       </c>
       <c r="D33" s="37" t="n">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Bron: blad 'M2-Subsidie' F21:G23. Werkt als derde plafond naast percentage en maximumbedrag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>ENERGIE- EN FINANCIELE PARAMETERS</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Kale dieselprijs [€/l]</t>
-        </is>
-      </c>
-      <c r="D38" s="33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Parameters D4</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Accijns diesel [€/l]</t>
-        </is>
-      </c>
-      <c r="D39" s="33" t="n">
-        <v>0.5163</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Parameters D5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Inkoopprijs netstroom [€/kWh]</t>
-        </is>
-      </c>
-      <c r="D40" s="33" t="n">
-        <v>0.21537</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Parameters D6</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Prijs eigen opwek [€/kWh]</t>
-        </is>
-      </c>
-      <c r="D41" s="33" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Parameters J47</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Fractie eigen opwek</t>
-        </is>
-      </c>
-      <c r="D42" s="37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Parameters J46</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Rente</t>
-        </is>
-      </c>
-      <c r="D43" s="37" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Parameters D30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Verzekering (% van bruto aanschaf)</t>
-        </is>
-      </c>
-      <c r="D44" s="37" t="n">
-        <v>0.03568675887</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Parameters D31</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Restwaarde na 7 jaar</t>
-        </is>
-      </c>
-      <c r="D45" s="37" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Parameters I21</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Economische levensduur [jaar]</t>
-        </is>
-      </c>
-      <c r="D46" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Input-Output Module D36</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Jaarlijkse stijging dieselprijs</t>
-        </is>
-      </c>
-      <c r="D47" s="37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Parameters I31</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Jaarlijkse stijging energiekosten</t>
-        </is>
-      </c>
-      <c r="D48" s="37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Parameters I32</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -2499,14 +2335,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F41"/>
+  <dimension ref="B1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2519,14 +2354,14 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Rekent live mee met blad Model. Alleen de eerste kolom is invoer.</t>
+          <t>Terugverdientijd inclusief restwaarde. Alleen de eerste kolom is invoer.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>A. KILOMETERS PER TRUCK PER JAAR</t>
+          <t>A. KILOMETERS — km per truck per jaar</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -2534,17 +2369,17 @@
       <c r="E4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="35" t="inlineStr">
-        <is>
-          <t>km per jaar</t>
-        </is>
-      </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>km per truck per jaar</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>Besparing per jaar</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>Terugverdientijd [jaar]</t>
         </is>
@@ -2554,12 +2389,12 @@
       <c r="B6" s="7" t="n">
         <v>60000</v>
       </c>
-      <c r="C6" s="21">
-        <f>(B6*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B6*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
-        <v/>
-      </c>
-      <c r="D6" s="39">
-        <f>IF(C6&lt;=0,"nooit",Model!$C$56/C6)</f>
+      <c r="C6" s="15">
+        <f>(B6*(Model!$C$21*Model!$C$22+0.025*0.73-Model!$C$53*Model!$C$26)+(Model!$C$30*(Model!$C$31-Model!$C$32)+Model!$C$33*(Model!$C$34-Model!$C$35)+Model!$C$36-Model!$C$37-Model!$C$38))*Model!$C$7+B6*Model!$C$53*Model!$C$7*Model!$C$47*(1-Model!$C$48)+Model!$C$106</f>
+        <v/>
+      </c>
+      <c r="D6" s="38">
+        <f>IF(C6&lt;=0,"nooit",Model!$C$74/C6)</f>
         <v/>
       </c>
     </row>
@@ -2567,12 +2402,12 @@
       <c r="B7" s="7" t="n">
         <v>80000</v>
       </c>
-      <c r="C7" s="21">
-        <f>(B7*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B7*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
-        <v/>
-      </c>
-      <c r="D7" s="39">
-        <f>IF(C7&lt;=0,"nooit",Model!$C$56/C7)</f>
+      <c r="C7" s="15">
+        <f>(B7*(Model!$C$21*Model!$C$22+0.025*0.73-Model!$C$53*Model!$C$26)+(Model!$C$30*(Model!$C$31-Model!$C$32)+Model!$C$33*(Model!$C$34-Model!$C$35)+Model!$C$36-Model!$C$37-Model!$C$38))*Model!$C$7+B7*Model!$C$53*Model!$C$7*Model!$C$47*(1-Model!$C$48)+Model!$C$106</f>
+        <v/>
+      </c>
+      <c r="D7" s="38">
+        <f>IF(C7&lt;=0,"nooit",Model!$C$74/C7)</f>
         <v/>
       </c>
     </row>
@@ -2580,12 +2415,12 @@
       <c r="B8" s="7" t="n">
         <v>100000</v>
       </c>
-      <c r="C8" s="21">
-        <f>(B8*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B8*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
-        <v/>
-      </c>
-      <c r="D8" s="39">
-        <f>IF(C8&lt;=0,"nooit",Model!$C$56/C8)</f>
+      <c r="C8" s="15">
+        <f>(B8*(Model!$C$21*Model!$C$22+0.025*0.73-Model!$C$53*Model!$C$26)+(Model!$C$30*(Model!$C$31-Model!$C$32)+Model!$C$33*(Model!$C$34-Model!$C$35)+Model!$C$36-Model!$C$37-Model!$C$38))*Model!$C$7+B8*Model!$C$53*Model!$C$7*Model!$C$47*(1-Model!$C$48)+Model!$C$106</f>
+        <v/>
+      </c>
+      <c r="D8" s="38">
+        <f>IF(C8&lt;=0,"nooit",Model!$C$74/C8)</f>
         <v/>
       </c>
     </row>
@@ -2593,12 +2428,12 @@
       <c r="B9" s="7" t="n">
         <v>120000</v>
       </c>
-      <c r="C9" s="21">
-        <f>(B9*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B9*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
-        <v/>
-      </c>
-      <c r="D9" s="39">
-        <f>IF(C9&lt;=0,"nooit",Model!$C$56/C9)</f>
+      <c r="C9" s="15">
+        <f>(B9*(Model!$C$21*Model!$C$22+0.025*0.73-Model!$C$53*Model!$C$26)+(Model!$C$30*(Model!$C$31-Model!$C$32)+Model!$C$33*(Model!$C$34-Model!$C$35)+Model!$C$36-Model!$C$37-Model!$C$38))*Model!$C$7+B9*Model!$C$53*Model!$C$7*Model!$C$47*(1-Model!$C$48)+Model!$C$106</f>
+        <v/>
+      </c>
+      <c r="D9" s="38">
+        <f>IF(C9&lt;=0,"nooit",Model!$C$74/C9)</f>
         <v/>
       </c>
     </row>
@@ -2606,12 +2441,12 @@
       <c r="B10" s="7" t="n">
         <v>150000</v>
       </c>
-      <c r="C10" s="21">
-        <f>(B10*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B10*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
-        <v/>
-      </c>
-      <c r="D10" s="39">
-        <f>IF(C10&lt;=0,"nooit",Model!$C$56/C10)</f>
+      <c r="C10" s="15">
+        <f>(B10*(Model!$C$21*Model!$C$22+0.025*0.73-Model!$C$53*Model!$C$26)+(Model!$C$30*(Model!$C$31-Model!$C$32)+Model!$C$33*(Model!$C$34-Model!$C$35)+Model!$C$36-Model!$C$37-Model!$C$38))*Model!$C$7+B10*Model!$C$53*Model!$C$7*Model!$C$47*(1-Model!$C$48)+Model!$C$106</f>
+        <v/>
+      </c>
+      <c r="D10" s="38">
+        <f>IF(C10&lt;=0,"nooit",Model!$C$74/C10)</f>
         <v/>
       </c>
     </row>
@@ -2619,351 +2454,393 @@
       <c r="B11" s="7" t="n">
         <v>180000</v>
       </c>
-      <c r="C11" s="21">
-        <f>(B11*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B11*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
-        <v/>
-      </c>
-      <c r="D11" s="39">
-        <f>IF(C11&lt;=0,"nooit",Model!$C$56/C11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C12" s="21">
-        <f>(B12*((Model!$C$12*Model!$C$15+Model!$C$20+Model!$C$33)-(Model!$C$32*Model!$C$19+Model!$C$21+Model!$C$34))-Model!$C$22)*Model!$C$7+B12*Model!$C$32*Model!$C$7*Model!$C$84*(1-Model!$C$85)+Model!$C$102</f>
-        <v/>
-      </c>
-      <c r="D12" s="39">
-        <f>IF(C12&lt;=0,"nooit",Model!$C$56/C12)</f>
-        <v/>
+      <c r="C11" s="15">
+        <f>(B11*(Model!$C$21*Model!$C$22+0.025*0.73-Model!$C$53*Model!$C$26)+(Model!$C$30*(Model!$C$31-Model!$C$32)+Model!$C$33*(Model!$C$34-Model!$C$35)+Model!$C$36-Model!$C$37-Model!$C$38))*Model!$C$7+B11*Model!$C$53*Model!$C$7*Model!$C$47*(1-Model!$C$48)+Model!$C$106</f>
+        <v/>
+      </c>
+      <c r="D11" s="38">
+        <f>IF(C11&lt;=0,"nooit",Model!$C$74/C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>B. STROOMPRIJS — € per kWh</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>€ per kWh</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>Besparing per jaar</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>Terugverdientijd [jaar]</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>B. GEMENGDE STROOMPRIJS</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
+      <c r="B15" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C15" s="15">
+        <f>Model!$C$112+(Model!$C$26-B15)*Model!$C$8*Model!$C$53*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D15" s="38">
+        <f>IF(C15&lt;=0,"nooit",Model!$C$74/C15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>€ per kWh</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
-        <is>
-          <t>Besparing per jaar</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
-          <t>Terugverdientijd [jaar]</t>
-        </is>
+      <c r="B16" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" s="15">
+        <f>Model!$C$112+(Model!$C$26-B16)*Model!$C$8*Model!$C$53*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D16" s="38">
+        <f>IF(C16&lt;=0,"nooit",Model!$C$74/C16)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="C17" s="21">
-        <f>Model!$C$105+(Model!$C$19-B17)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D17" s="39">
-        <f>IF(C17&lt;=0,"nooit",Model!$C$56/C17)</f>
+        <v>0.14</v>
+      </c>
+      <c r="C17" s="15">
+        <f>Model!$C$112+(Model!$C$26-B17)*Model!$C$8*Model!$C$53*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D17" s="38">
+        <f>IF(C17&lt;=0,"nooit",Model!$C$74/C17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C18" s="21">
-        <f>Model!$C$105+(Model!$C$19-B18)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D18" s="39">
-        <f>IF(C18&lt;=0,"nooit",Model!$C$56/C18)</f>
+        <v>0.18</v>
+      </c>
+      <c r="C18" s="15">
+        <f>Model!$C$112+(Model!$C$26-B18)*Model!$C$8*Model!$C$53*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D18" s="38">
+        <f>IF(C18&lt;=0,"nooit",Model!$C$74/C18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="12" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C19" s="21">
-        <f>Model!$C$105+(Model!$C$19-B19)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D19" s="39">
-        <f>IF(C19&lt;=0,"nooit",Model!$C$56/C19)</f>
+        <v>0.2154</v>
+      </c>
+      <c r="C19" s="15">
+        <f>Model!$C$112+(Model!$C$26-B19)*Model!$C$8*Model!$C$53*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D19" s="38">
+        <f>IF(C19&lt;=0,"nooit",Model!$C$74/C19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C20" s="21">
-        <f>Model!$C$105+(Model!$C$19-B20)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D20" s="39">
-        <f>IF(C20&lt;=0,"nooit",Model!$C$56/C20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="12" t="n">
-        <v>0.2154</v>
-      </c>
-      <c r="C21" s="21">
-        <f>Model!$C$105+(Model!$C$19-B21)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D21" s="39">
-        <f>IF(C21&lt;=0,"nooit",Model!$C$56/C21)</f>
+        <v>0.3</v>
+      </c>
+      <c r="C20" s="15">
+        <f>Model!$C$112+(Model!$C$26-B20)*Model!$C$8*Model!$C$53*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D20" s="38">
+        <f>IF(C20&lt;=0,"nooit",Model!$C$74/C20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C22" s="21">
-        <f>Model!$C$105+(Model!$C$19-B22)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D22" s="39">
-        <f>IF(C22&lt;=0,"nooit",Model!$C$56/C22)</f>
-        <v/>
-      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>C. DIESELVERBRUIK — 1 op ...</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C23" s="21">
-        <f>Model!$C$105+(Model!$C$19-B23)*Model!$C$8*Model!$C$32*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D23" s="39">
-        <f>IF(C23&lt;=0,"nooit",Model!$C$56/C23)</f>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>1 op ...</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>Besparing per jaar</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>Terugverdientijd [jaar]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C24" s="15">
+        <f>Model!$C$112+(1/B24-Model!$C$21)*Model!$C$8*Model!$C$22*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D24" s="38">
+        <f>IF(C24&lt;=0,"nooit",Model!$C$74/C24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C25" s="15">
+        <f>Model!$C$112+(1/B25-Model!$C$21)*Model!$C$8*Model!$C$22*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D25" s="38">
+        <f>IF(C25&lt;=0,"nooit",Model!$C$74/C25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>C. DIESELVERBRUIK — 1 OP ...</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
+      <c r="B26" s="10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C26" s="15">
+        <f>Model!$C$112+(1/B26-Model!$C$21)*Model!$C$8*Model!$C$22*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D26" s="38">
+        <f>IF(C26&lt;=0,"nooit",Model!$C$74/C26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>1 op ...</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="B27" s="10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C27" s="15">
+        <f>Model!$C$112+(1/B27-Model!$C$21)*Model!$C$8*Model!$C$22*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D27" s="38">
+        <f>IF(C27&lt;=0,"nooit",Model!$C$74/C27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C28" s="15">
+        <f>Model!$C$112+(1/B28-Model!$C$21)*Model!$C$8*Model!$C$22*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D28" s="38">
+        <f>IF(C28&lt;=0,"nooit",Model!$C$74/C28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="15">
+        <f>Model!$C$112+(1/B29-Model!$C$21)*Model!$C$8*Model!$C$22*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D29" s="38">
+        <f>IF(C29&lt;=0,"nooit",Model!$C$74/C29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>D. RESTWAARDE E-TRUCK — € per truck</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>€ per truck</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
         <is>
           <t>Besparing per jaar</t>
         </is>
       </c>
-      <c r="D27" s="35" t="inlineStr">
+      <c r="D32" s="34" t="inlineStr">
         <is>
           <t>Terugverdientijd [jaar]</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C28" s="21">
-        <f>Model!$C$105+(1/B28-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D28" s="39">
-        <f>IF(C28&lt;=0,"nooit",Model!$C$56/C28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C29" s="21">
-        <f>Model!$C$105+(1/B29-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D29" s="39">
-        <f>IF(C29&lt;=0,"nooit",Model!$C$56/C29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C30" s="21">
-        <f>Model!$C$105+(1/B30-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D30" s="39">
-        <f>IF(C30&lt;=0,"nooit",Model!$C$56/C30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C31" s="21">
-        <f>Model!$C$105+(1/B31-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D31" s="39">
-        <f>IF(C31&lt;=0,"nooit",Model!$C$56/C31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C32" s="21">
-        <f>Model!$C$105+(1/B32-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D32" s="39">
-        <f>IF(C32&lt;=0,"nooit",Model!$C$56/C32)</f>
-        <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C33" s="21">
-        <f>Model!$C$105+(1/B33-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D33" s="39">
-        <f>IF(C33&lt;=0,"nooit",Model!$C$56/C33)</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="15">
+        <f>Model!$C$112+(B33-Model!$C$16)*Model!$C$7/Model!$C$11</f>
+        <v/>
+      </c>
+      <c r="D33" s="38">
+        <f>IF(C33&lt;=0,"nooit",Model!$C$74/C33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" s="21">
-        <f>Model!$C$105+(1/B34-Model!$C$12)*Model!$C$8*Model!$C$15*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D34" s="39">
-        <f>IF(C34&lt;=0,"nooit",Model!$C$56/C34)</f>
+        <v>20000</v>
+      </c>
+      <c r="C34" s="15">
+        <f>Model!$C$112+(B34-Model!$C$16)*Model!$C$7/Model!$C$11</f>
+        <v/>
+      </c>
+      <c r="D34" s="38">
+        <f>IF(C34&lt;=0,"nooit",Model!$C$74/C34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C35" s="15">
+        <f>Model!$C$112+(B35-Model!$C$16)*Model!$C$7/Model!$C$11</f>
+        <v/>
+      </c>
+      <c r="D35" s="38">
+        <f>IF(C35&lt;=0,"nooit",Model!$C$74/C35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="9" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C36" s="15">
+        <f>Model!$C$112+(B36-Model!$C$16)*Model!$C$7/Model!$C$11</f>
+        <v/>
+      </c>
+      <c r="D36" s="38">
+        <f>IF(C36&lt;=0,"nooit",Model!$C$74/C36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>D. ONDERNEMINGSGROOTTE</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>Grootte</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>AanZET totaal</t>
-        </is>
-      </c>
-      <c r="D38" s="35" t="inlineStr">
-        <is>
-          <t>Extra investering</t>
-        </is>
-      </c>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="B37" s="9" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C37" s="15">
+        <f>Model!$C$112+(B37-Model!$C$16)*Model!$C$7/Model!$C$11</f>
+        <v/>
+      </c>
+      <c r="D37" s="38">
+        <f>IF(C37&lt;=0,"nooit",Model!$C$74/C37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>E. ONDERHOUD ELEKTRISCH — € per jaar</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>€ per jaar</t>
+        </is>
+      </c>
+      <c r="C40" s="34" t="inlineStr">
+        <is>
+          <t>Besparing per jaar</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
         <is>
           <t>Terugverdientijd [jaar]</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Klein</t>
-        </is>
-      </c>
-      <c r="C39" s="21">
-        <f>MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B39,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D39" s="21">
-        <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B39,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B39),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B39,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
-        <v/>
-      </c>
-      <c r="E39" s="39">
-        <f>IF(Model!$C$105&lt;=0,"nooit",D39/Model!$C$105)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Middelgroot</t>
-        </is>
-      </c>
-      <c r="C40" s="21">
-        <f>MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B40,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D40" s="21">
-        <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B40,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B40),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B40,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
-        <v/>
-      </c>
-      <c r="E40" s="39">
-        <f>IF(Model!$C$105&lt;=0,"nooit",D40/Model!$C$105)</f>
-        <v/>
-      </c>
-    </row>
     <row r="41">
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Groot</t>
-        </is>
-      </c>
-      <c r="C41" s="21">
-        <f>MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B41,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)*Model!$C$7</f>
-        <v/>
-      </c>
-      <c r="D41" s="21">
-        <f>(Model!$C$42-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B41,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42)-MAX(0,IF(Model!$C$25="Ja",Model!$C$13,Model!$C$42)-MIN(Model!$C$13*SUMIFS('Panteia-parameters'!$E$16:$E$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),SUMIFS('Panteia-parameters'!$F$16:$F$27,'Panteia-parameters'!$C$16:$C$27,Model!$C$30,'Panteia-parameters'!$D$16:$D$27,B41),INDEX('Panteia-parameters'!$D$31:$D$33,MATCH(B41,'Panteia-parameters'!$C$31:$C$33,0))*Model!$C$42))*Model!$C$24*Model!$C$23)*Model!$C$7+Model!$C$55</f>
-        <v/>
-      </c>
-      <c r="E41" s="39">
-        <f>IF(Model!$C$105&lt;=0,"nooit",D41/Model!$C$105)</f>
+      <c r="B41" s="9" t="n">
+        <v>4600</v>
+      </c>
+      <c r="C41" s="15">
+        <f>Model!$C$112-(B41-Model!$C$37)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D41" s="38">
+        <f>IF(C41&lt;=0,"nooit",Model!$C$74/C41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="9" t="n">
+        <v>6200</v>
+      </c>
+      <c r="C42" s="15">
+        <f>Model!$C$112-(B42-Model!$C$37)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D42" s="38">
+        <f>IF(C42&lt;=0,"nooit",Model!$C$74/C42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="9" t="n">
+        <v>7740</v>
+      </c>
+      <c r="C43" s="15">
+        <f>Model!$C$112-(B43-Model!$C$37)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D43" s="38">
+        <f>IF(C43&lt;=0,"nooit",Model!$C$74/C43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C44" s="15">
+        <f>Model!$C$112-(B44-Model!$C$37)*Model!$C$7</f>
+        <v/>
+      </c>
+      <c r="D44" s="38">
+        <f>IF(C44&lt;=0,"nooit",Model!$C$74/C44)</f>
         <v/>
       </c>
     </row>

--- a/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
+++ b/docs/subsidies/AanZET TCO-model elektrische trucks.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Opgave Kwekerij Baas. Werkelijke dagritten wijzen op 117.000 tot 142.000 — zie doc §6e</t>
+          <t>Opgave Kwekerij Baas, bevestigd 21-08-2026</t>
         </is>
       </c>
     </row>
